--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -739,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="B2:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -747,7 +747,6 @@
     <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5738,22 +5737,34 @@
       </c>
       <c r="K3" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L3" s="32" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L3" s="32" t="n">
+        <v>1</v>
+      </c>
       <c r="M3" s="33">
         <f>IF(K3="Done",1,IF(L3="",0,MIN(1,L3)))</f>
         <v/>
       </c>
       <c r="N3" s="31" t="n"/>
-      <c r="O3" s="34" t="n"/>
+      <c r="O3" s="34" t="n">
+        <v>46318</v>
+      </c>
       <c r="P3" s="29">
         <f>IF(K3="Done",IF(O3="","Done",IF(J3="","Done",IF(O3&lt;=J3,"On time","Late"))),IF(K3="Blocked","BLOCKED",IF(I3="","",IF(TODAY()&gt;J3,"OVERDUE",IF(TODAY()&gt;=I3,"Active","Upcoming")))))</f>
         <v/>
       </c>
-      <c r="Q3" s="31" t="n"/>
-      <c r="R3" s="31" t="n"/>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>commit 79c4389 (branch foundation)</t>
+        </is>
+      </c>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, README, CONTRIBUTING, ADR-0000/0001, design + runbook templates, coding/testing/API/git standards</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="29" t="inlineStr">
@@ -5802,22 +5813,34 @@
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L4" s="32" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L4" s="32" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" s="33">
         <f>IF(K4="Done",1,IF(L4="",0,MIN(1,L4)))</f>
         <v/>
       </c>
       <c r="N4" s="31" t="n"/>
-      <c r="O4" s="34" t="n"/>
+      <c r="O4" s="34" t="n">
+        <v>46318</v>
+      </c>
       <c r="P4" s="29">
         <f>IF(K4="Done",IF(O4="","Done",IF(J4="","Done",IF(O4&lt;=J4,"On time","Late"))),IF(K4="Blocked","BLOCKED",IF(I4="","",IF(TODAY()&gt;J4,"OVERDUE",IF(TODAY()&gt;=I4,"Active","Upcoming")))))</f>
         <v/>
       </c>
-      <c r="Q4" s="31" t="n"/>
-      <c r="R4" s="31" t="n"/>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>commit 79c4389 (branch foundation)</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>docs/slo/template.md (burn-rate alerting) + docs/slo/error-budget-policy.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>terraform plan/apply green from CI; state in S3 + DynamoDB lock</t>
+          <t>terraform plan/apply green from CI; state in S3 with native locking (ADR-0002)</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -5889,10 +5889,12 @@
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L5" s="32" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L5" s="32" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M5" s="33">
         <f>IF(K5="Done",1,IF(L5="",0,MIN(1,L5)))</f>
         <v/>
@@ -5903,8 +5905,16 @@
         <f>IF(K5="Done",IF(O5="","Done",IF(J5="","Done",IF(O5&lt;=J5,"On time","Late"))),IF(K5="Blocked","BLOCKED",IF(I5="","",IF(TODAY()&gt;J5,"OVERDUE",IF(TODAY()&gt;=I5,"Active","Upcoming")))))</f>
         <v/>
       </c>
-      <c r="Q5" s="31" t="n"/>
-      <c r="R5" s="31" t="n"/>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>commit 1bea340 (branch mb-t03-terraform-baseline)</t>
+        </is>
+      </c>
+      <c r="R5" s="31" t="inlineStr">
+        <is>
+          <t>Done: modules, dev/prod envs, 37 terraform tests, fmt/validate/tflint/trivy clean. Remaining: first apply to AWS (needs an AWS account) and plan/apply from CI (MB-T05). DynamoDB lock replaced by S3-native locking per ADR-0002.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5757,12 +5757,12 @@
       </c>
       <c r="Q3" s="31" t="inlineStr">
         <is>
-          <t>commit 79c4389 (branch foundation)</t>
+          <t>commit 19024d4 (branch foundation)</t>
         </is>
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>CLAUDE.md, README, CONTRIBUTING, ADR-0000/0001, design + runbook templates, coding/testing/API/git standards</t>
+          <t>Engineering rules, README, CONTRIBUTING, ADR-0000/0001, design + runbook templates, coding/testing/API/git standards</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>commit 79c4389 (branch foundation)</t>
+          <t>commit 19024d4 (branch foundation)</t>
         </is>
       </c>
       <c r="R4" s="31" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>commit 1bea340 (branch mb-t03-terraform-baseline)</t>
+          <t>commit 4d92693 (branch mb-t03-terraform-baseline)</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -6027,10 +6027,12 @@
       </c>
       <c r="K7" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L7" s="32" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L7" s="32" t="n">
+        <v>0.7</v>
+      </c>
       <c r="M7" s="33">
         <f>IF(K7="Done",1,IF(L7="",0,MIN(1,L7)))</f>
         <v/>
@@ -6041,8 +6043,16 @@
         <f>IF(K7="Done",IF(O7="","Done",IF(J7="","Done",IF(O7&lt;=J7,"On time","Late"))),IF(K7="Blocked","BLOCKED",IF(I7="","",IF(TODAY()&gt;J7,"OVERDUE",IF(TODAY()&gt;=I7,"Active","Upcoming")))))</f>
         <v/>
       </c>
-      <c r="Q7" s="31" t="n"/>
-      <c r="R7" s="31" t="n"/>
+      <c r="Q7" s="31" t="inlineStr">
+        <is>
+          <t>https://github.com/mhrj7/meterbook/pull/3</t>
+        </is>
+      </c>
+      <c r="R7" s="31" t="inlineStr">
+        <is>
+          <t>Done: ci.yml (Terraform checks, Gitleaks, actionlint, single ci check), reusable container.yml (Trivy gate, SBOM, cosign), Terraform plan/apply via OIDC, SHA-pinned actions, Dependabot, ADR-0003. Remaining: green CI run as evidence, pipeline time measured, CRITICAL-CVE gate exercised by the first service image.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="L7" s="32" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="M7" s="33">
         <f>IF(K7="Done",1,IF(L7="",0,MIN(1,L7)))</f>
@@ -6045,12 +6045,12 @@
       </c>
       <c r="Q7" s="31" t="inlineStr">
         <is>
-          <t>https://github.com/mhrj7/meterbook/pull/3</t>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39905115436</t>
         </is>
       </c>
       <c r="R7" s="31" t="inlineStr">
         <is>
-          <t>Done: ci.yml (Terraform checks, Gitleaks, actionlint, single ci check), reusable container.yml (Trivy gate, SBOM, cosign), Terraform plan/apply via OIDC, SHA-pinned actions, Dependabot, ADR-0003. Remaining: green CI run as evidence, pipeline time measured, CRITICAL-CVE gate exercised by the first service image.</t>
+          <t>Green CI run on PR #3: 3.3 min wall clock (Terraform job 3.0 min). Done: ci.yml (Terraform fmt/validate/test/tflint/trivy, Gitleaks, actionlint, single ci check), reusable container.yml (Trivy CRITICAL gate, SBOM, cosign), Terraform plan/apply via OIDC, SHA-pinned actions, Dependabot, ADR-0003. Remaining: CRITICAL-CVE gate exercised by the first service image (MB-T07).</t>
         </is>
       </c>
     </row>
@@ -11585,13 +11585,23 @@
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L9" s="34" t="n"/>
-      <c r="M9" s="31" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" s="34" t="n">
+        <v>46318</v>
+      </c>
+      <c r="M9" s="31" t="inlineStr">
+        <is>
+          <t>0 findings across full history</t>
+        </is>
+      </c>
       <c r="N9" s="31" t="n"/>
-      <c r="O9" s="31" t="n"/>
+      <c r="O9" s="31" t="inlineStr">
+        <is>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39905115436</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -14195,7 +14205,9 @@
           <t>min</t>
         </is>
       </c>
-      <c r="H5" s="39" t="n"/>
+      <c r="H5" s="39" t="n">
+        <v>3.3</v>
+      </c>
       <c r="I5" s="29">
         <f>IF(H5="","PENDING",IF(E5="&lt;=",IF(H5&lt;=F5,"PASS","FAIL"),IF(H5&gt;=F5,"PASS","FAIL")))</f>
         <v/>
@@ -14205,10 +14217,24 @@
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="K5" s="31" t="n"/>
-      <c r="L5" s="34" t="n"/>
-      <c r="M5" s="31" t="n"/>
-      <c r="N5" s="31" t="n"/>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>39905115436</t>
+        </is>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>46318</v>
+      </c>
+      <c r="M5" s="31" t="inlineStr">
+        <is>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39905115436</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>Wall clock from run created to last job completed, PR #3.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5963,10 +5963,12 @@
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="L6" s="32" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M6" s="33">
         <f>IF(K6="Done",1,IF(L6="",0,MIN(1,L6)))</f>
         <v/>
@@ -5977,8 +5979,16 @@
         <f>IF(K6="Done",IF(O6="","Done",IF(J6="","Done",IF(O6&lt;=J6,"On time","Late"))),IF(K6="Blocked","BLOCKED",IF(I6="","",IF(TODAY()&gt;J6,"OVERDUE",IF(TODAY()&gt;=I6,"Active","Upcoming")))))</f>
         <v/>
       </c>
-      <c r="Q6" s="31" t="n"/>
-      <c r="R6" s="31" t="n"/>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>https://github.com/mhrj7/meterbook/pull/4</t>
+        </is>
+      </c>
+      <c r="R6" s="31" t="inlineStr">
+        <is>
+          <t>Done: app-secrets module (KMS, empty shells, Pod Identity ESO role, exact-ARN policy), platform-secrets Helm chart, ADR-0004, runbook; 7 terraform + 18 chart tests; kind end-to-end test (runtime read, rotation, namespace isolation) in CI. Remaining: green e2e evidence, then real AWS once dev is applied and ESO is installed via ArgoCD (MB-T06).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="L5" s="32" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M5" s="33">
         <f>IF(K5="Done",1,IF(L5="",0,MIN(1,L5)))</f>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>commit 4d92693 (branch mb-t03-terraform-baseline)</t>
+          <t>https://github.com/mhrj7/meterbook/pull/5</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
-          <t>Done: modules, dev/prod envs, 37 terraform tests, fmt/validate/tflint/trivy clean. Remaining: first apply to AWS (needs an AWS account) and plan/apply from CI (MB-T05). DynamoDB lock replaced by S3-native locking per ADR-0002.</t>
+          <t>CI-owned bootstrap (state bucket, OIDC provider, plan/apply roles via import blocks), apply-verify-destroy workflow, verify-dev.sh (AWS API checks), DB subnets isolated from internet, eu-north-1. GitHub OIDC provider created in AWS. Remaining: apply role (needs owner approval), bootstrap + dev apply from CI (blocked until AWS finishes verifying the new account).</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="L6" s="32" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M6" s="33">
         <f>IF(K6="Done",1,IF(L6="",0,MIN(1,L6)))</f>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
-          <t>https://github.com/mhrj7/meterbook/pull/4</t>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39912053895</t>
         </is>
       </c>
       <c r="R6" s="31" t="inlineStr">
         <is>
-          <t>Done: app-secrets module (KMS, empty shells, Pod Identity ESO role, exact-ARN policy), platform-secrets Helm chart, ADR-0004, runbook; 7 terraform + 18 chart tests; kind end-to-end test (runtime read, rotation, namespace isolation) in CI. Remaining: green e2e evidence, then real AWS once dev is applied and ESO is installed via ArgoCD (MB-T06).</t>
+          <t>Green CI incl. kind end-to-end (4/4: delivery, runtime read by a pod, rotation in 3s, namespace isolation) after fixing a false-green CI step and a moto crash. Remaining: verify on real AWS (secrets, ESO role, Pod Identity) once the AWS account finishes verification and dev is applied.</t>
         </is>
       </c>
     </row>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5907,12 +5907,12 @@
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>https://github.com/mhrj7/meterbook/pull/5</t>
+          <t>https://github.com/mhrj7/meterbook/pull/7</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
-          <t>CI-owned bootstrap (state bucket, OIDC provider, plan/apply roles via import blocks), apply-verify-destroy workflow, verify-dev.sh (AWS API checks), DB subnets isolated from internet, eu-north-1. GitHub OIDC provider created in AWS. Remaining: apply role (needs owner approval), bootstrap + dev apply from CI (blocked until AWS finishes verifying the new account).</t>
+          <t>In AWS (eu-north-1): GitHub OIDC provider and meterbook-terraform-apply role created; trust fixed to GitHub's immutable OIDC subjects after the first bootstrap run was rejected. GitHub environments dev/production limited to main. Stack merged to main (PRs #1-#6). Remaining: bootstrap run green (state bucket, plan role), then dev apply-verify-destroy once AWS finishes verifying the new account.</t>
         </is>
       </c>
     </row>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -5889,30 +5889,32 @@
       </c>
       <c r="K5" s="31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L5" s="32" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="M5" s="33">
         <f>IF(K5="Done",1,IF(L5="",0,MIN(1,L5)))</f>
         <v/>
       </c>
       <c r="N5" s="31" t="n"/>
-      <c r="O5" s="34" t="n"/>
+      <c r="O5" s="34" t="n">
+        <v>46318</v>
+      </c>
       <c r="P5" s="29">
         <f>IF(K5="Done",IF(O5="","Done",IF(J5="","Done",IF(O5&lt;=J5,"On time","Late"))),IF(K5="Blocked","BLOCKED",IF(I5="","",IF(TODAY()&gt;J5,"OVERDUE",IF(TODAY()&gt;=I5,"Active","Upcoming")))))</f>
         <v/>
       </c>
       <c r="Q5" s="31" t="inlineStr">
         <is>
-          <t>https://github.com/mhrj7/meterbook/pull/7</t>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39939409530</t>
         </is>
       </c>
       <c r="R5" s="31" t="inlineStr">
         <is>
-          <t>In AWS (eu-north-1): GitHub OIDC provider and meterbook-terraform-apply role created; trust fixed to GitHub's immutable OIDC subjects after the first bootstrap run was rejected. GitHub environments dev/production limited to main. Stack merged to main (PRs #1-#6). Remaining: bootstrap run green (state bucket, plan role), then dev apply-verify-destroy once AWS finishes verifying the new account.</t>
+          <t>Dev applied from CI on real AWS (eu-north-1): apply 12m54s, 35/35 baseline checks passed (state in S3 with native locking, EKS private+audited+KMS, nodes ACTIVE, RDS private/encrypted/TLS, buckets locked down, DB subnets without internet route), destroy removed 99 resources, 0 left. Fixed on the way: GitHub immutable OIDC subjects, Spot unavailable on new accounts, Free-plan instance types (dev uses m7i-flex.large), secrets recovery window on disposable envs.</t>
         </is>
       </c>
     </row>
@@ -5963,30 +5965,32 @@
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L6" s="32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M6" s="33">
         <f>IF(K6="Done",1,IF(L6="",0,MIN(1,L6)))</f>
         <v/>
       </c>
       <c r="N6" s="31" t="n"/>
-      <c r="O6" s="34" t="n"/>
+      <c r="O6" s="34" t="n">
+        <v>46318</v>
+      </c>
       <c r="P6" s="29">
         <f>IF(K6="Done",IF(O6="","Done",IF(J6="","Done",IF(O6&lt;=J6,"On time","Late"))),IF(K6="Blocked","BLOCKED",IF(I6="","",IF(TODAY()&gt;J6,"OVERDUE",IF(TODAY()&gt;=I6,"Active","Upcoming")))))</f>
         <v/>
       </c>
       <c r="Q6" s="31" t="inlineStr">
         <is>
-          <t>https://github.com/mhrj7/meterbook/actions/runs/39912053895</t>
+          <t>https://github.com/mhrj7/meterbook/actions/runs/39939409530</t>
         </is>
       </c>
       <c r="R6" s="31" t="inlineStr">
         <is>
-          <t>Green CI incl. kind end-to-end (4/4: delivery, runtime read by a pod, rotation in 3s, namespace isolation) after fixing a false-green CI step and a moto crash. Remaining: verify on real AWS (secrets, ESO role, Pod Identity) once the AWS account finishes verification and dev is applied.</t>
+          <t>No secrets in git (Gitleaks, every run). Pods read secrets at runtime: kind end-to-end in CI (delivery, runtime read, rotation in 3s, namespace isolation; run 39912053895). On real AWS: 3 KMS-encrypted app secrets, ESO bound by Pod Identity, IAM simulation allows reading app secrets and denies other secrets and writes. ESO install on EKS follows with ArgoCD in MB-T06.</t>
         </is>
       </c>
     </row>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="995">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -765,21 +765,27 @@
     <t xml:space="preserve">SSO e2e test passes with a test IdP</t>
   </si>
   <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40065555690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoD: SSO e2e in a real browser through a SAML IdP passes in CI on every identity change (TC-PLT-001; run 40065295770): tenant, SAML connection, SCIM token and user set up through the APIs; SSO sign-in lands in the tenant; JIT users join the tenant; another tenant's IdP asserting a victim's email is refused; SCIM deactivation kills the session and blocks sign-in. On EKS (run 40065555690): Keycloak + identity per environment via ArgoCD, db-bootstrap, operator creates a tenant, RDS isolation; 78/78 checks, 107 resources applied and destroyed. Built: ADR-0007/0008, design doc, OpenAPI contract with Spectral + oasdiff in CI, Spring Boot 4.1 on Java 25, Keycloak adapter, tenants, SAML SSO connections, SCIM 2.0 Users/Groups, Idempotency-Key, 158 tests (97% line / 87% branch). Found and fixed: cross-tenant account takeover via link-by-email; SCIM secret in idempotency store; Keycloak 26.8 domain routing; JIT onboarding; ArgoCD subchart dependency; a false-green CI pipeline (pipefail). Evidence: docs/evidence/2026-10-24-identity-sso-and-eks.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB-T08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenant model org &gt; project &gt; env; Postgres row-level security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-tenant access test fails closed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Started</t>
   </si>
   <si>
-    <t xml:space="preserve">MB-T08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tenant model org &gt; project &gt; env; Postgres row-level security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-tenant access test fails closed</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB-T09</t>
   </si>
   <si>
@@ -1957,6 +1963,12 @@
   </si>
   <si>
     <t xml:space="preserve">Playwright + Testcontainers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAML SSO via Keycloak broker in Chromium (Playwright): tenant claim, sso login method, JIT, cross-tenant IdP refused, SCIM deactivation blocks sign-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40065295770</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-002</t>
@@ -4236,60 +4248,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4302,13 +4314,13 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6062,34 +6074,34 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6167,7 +6179,7 @@
       </c>
       <c r="E4" s="31" t="n">
         <f aca="false">COUNTIFS(Plan!$H$2:$H$600,A4,Plan!$K$2:$K$600,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="31" t="n">
         <f aca="false">SUMIF(Plan!$H$2:$H$600,A4,Plan!$G$2:$G$600)</f>
@@ -6589,7 +6601,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,B$4,Plan!$K$2:$K$600,"Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,C$4,Plan!$K$2:$K$600,"Done")</f>
@@ -6597,7 +6609,7 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">SUM(B8:C8)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6674,7 +6686,7 @@
       </c>
       <c r="B13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=B$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=C$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
@@ -6682,7 +6694,7 @@
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">SUM(B13:C13)</f>
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6691,7 +6703,7 @@
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">IFERROR(B13/B12,0)</f>
-        <v>0.373333333333333</v>
+        <v>0.506666666666667</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C13/C12,0)</f>
@@ -6699,7 +6711,7 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">IFERROR(D13/D12,0)</f>
-        <v>0.130232558139535</v>
+        <v>0.176744186046512</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6733,7 +6745,7 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Pass")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Pass")</f>
@@ -6741,7 +6753,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">SUM(B18:C18)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6784,7 +6796,7 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
@@ -6792,7 +6804,7 @@
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">SUM(B21:C21)</f>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6801,7 +6813,7 @@
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IFERROR((B17-B21)/B17,0)</f>
-        <v>0.157894736842105</v>
+        <v>0.210526315789474</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">IFERROR((C17-C21)/C17,0)</f>
@@ -6809,7 +6821,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">IFERROR((D17-D21)/D17,0)</f>
-        <v>0.0666666666666667</v>
+        <v>0.0888888888888889</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7138,7 +7150,7 @@
       </c>
       <c r="D47" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -7146,7 +7158,7 @@
       </c>
       <c r="F47" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Not Run")-COUNTIFS(Test_Cases!$C$2:$C$600,A47,Test_Cases!$K$2:$K$600,"Not Run",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8300,7 +8312,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2EF13051-3CF9-4CC6-97AA-61E41B14BAE2}</x14:id>
+          <x14:id>{B9133E3B-DA92-4DCB-9CEB-40B43A3957E8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8314,7 +8326,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{726F13C7-9760-4F3B-AD86-A2E6787E91CA}</x14:id>
+          <x14:id>{CD282A99-D9C3-4DD6-9C2B-29781978C26C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8328,7 +8340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C4612F98-9C25-455B-8013-AD2B45F84BB3}</x14:id>
+          <x14:id>{B013A9A5-C4CC-48C7-A022-F3FDC164D331}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8342,7 +8354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E0EAF713-712D-4C26-B8C5-6D1B386017FE}</x14:id>
+          <x14:id>{A2CFB084-B488-4DA7-9E76-7CA95595B5AE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8388,7 +8400,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2EF13051-3CF9-4CC6-97AA-61E41B14BAE2}">
+          <x14:cfRule type="dataBar" id="{B9133E3B-DA92-4DCB-9CEB-40B43A3957E8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8403,7 +8415,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{726F13C7-9760-4F3B-AD86-A2E6787E91CA}">
+          <x14:cfRule type="dataBar" id="{CD282A99-D9C3-4DD6-9C2B-29781978C26C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8418,7 +8430,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C4612F98-9C25-455B-8013-AD2B45F84BB3}">
+          <x14:cfRule type="dataBar" id="{B013A9A5-C4CC-48C7-A022-F3FDC164D331}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8433,7 +8445,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E0EAF713-712D-4C26-B8C5-6D1B386017FE}">
+          <x14:cfRule type="dataBar" id="{A2CFB084-B488-4DA7-9E76-7CA95595B5AE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8976,37 +8988,45 @@
         <v>46346</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="L9" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="L9" s="34" t="n">
+        <v>1</v>
+      </c>
       <c r="M9" s="35" t="n">
         <f aca="false">IF(K9="Done",1,IF(L9="",0,MIN(1,L9)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="33"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="36" t="n">
+        <v>46319</v>
+      </c>
       <c r="P9" s="31" t="str">
         <f aca="true">IF(K9="Done",IF(O9="","Done",IF(J9="","Done",IF(O9&lt;=J9,"On time","Late"))),IF(K9="Blocked","BLOCKED",IF(I9="","",IF(TODAY()&gt;J9,"OVERDUE",IF(TODAY()&gt;=I9,"Active","Upcoming")))))</f>
-        <v>Upcoming</v>
-      </c>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
+        <v>On time</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F10" s="31" t="s">
         <v>161</v>
@@ -9026,7 +9046,7 @@
         <v>46346</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35" t="n">
@@ -9044,19 +9064,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F11" s="31" t="s">
         <v>161</v>
@@ -9076,7 +9096,7 @@
         <v>46346</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="35" t="n">
@@ -9094,19 +9114,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F12" s="31" t="s">
         <v>168</v>
@@ -9126,7 +9146,7 @@
         <v>46353</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35" t="n">
@@ -9144,19 +9164,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>161</v>
@@ -9176,7 +9196,7 @@
         <v>46353</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="n">
@@ -9194,19 +9214,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F14" s="31" t="s">
         <v>161</v>
@@ -9226,7 +9246,7 @@
         <v>46353</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="n">
@@ -9244,19 +9264,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F15" s="31" t="s">
         <v>168</v>
@@ -9276,7 +9296,7 @@
         <v>46353</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="n">
@@ -9294,19 +9314,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F16" s="31" t="s">
         <v>161</v>
@@ -9326,7 +9346,7 @@
         <v>46353</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="n">
@@ -9344,22 +9364,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G17" s="31" t="n">
         <v>4</v>
@@ -9376,7 +9396,7 @@
         <v>46353</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35" t="n">
@@ -9394,7 +9414,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
@@ -9403,10 +9423,10 @@
         <v>165</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F18" s="31" t="s">
         <v>161</v>
@@ -9426,7 +9446,7 @@
         <v>46360</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="n">
@@ -9444,7 +9464,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -9453,10 +9473,10 @@
         <v>165</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F19" s="31" t="s">
         <v>161</v>
@@ -9476,7 +9496,7 @@
         <v>46360</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="n">
@@ -9494,7 +9514,7 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
@@ -9503,10 +9523,10 @@
         <v>165</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F20" s="31" t="s">
         <v>161</v>
@@ -9526,7 +9546,7 @@
         <v>46360</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="n">
@@ -9544,7 +9564,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
@@ -9553,10 +9573,10 @@
         <v>158</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F21" s="31" t="s">
         <v>161</v>
@@ -9576,7 +9596,7 @@
         <v>46367</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="n">
@@ -9594,7 +9614,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -9603,10 +9623,10 @@
         <v>158</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F22" s="31" t="s">
         <v>161</v>
@@ -9626,7 +9646,7 @@
         <v>46367</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="n">
@@ -9644,7 +9664,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -9653,10 +9673,10 @@
         <v>158</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>161</v>
@@ -9676,7 +9696,7 @@
         <v>46374</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="n">
@@ -9694,7 +9714,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -9703,10 +9723,10 @@
         <v>158</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F24" s="31" t="s">
         <v>161</v>
@@ -9726,7 +9746,7 @@
         <v>46381</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="n">
@@ -9744,7 +9764,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -9753,10 +9773,10 @@
         <v>158</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F25" s="31" t="s">
         <v>161</v>
@@ -9776,7 +9796,7 @@
         <v>46388</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="n">
@@ -9794,7 +9814,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -9803,10 +9823,10 @@
         <v>158</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F26" s="31" t="s">
         <v>161</v>
@@ -9826,7 +9846,7 @@
         <v>46388</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="n">
@@ -9844,7 +9864,7 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -9853,10 +9873,10 @@
         <v>158</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>161</v>
@@ -9876,7 +9896,7 @@
         <v>46395</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35" t="n">
@@ -9894,7 +9914,7 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -9903,10 +9923,10 @@
         <v>158</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F28" s="31" t="s">
         <v>168</v>
@@ -9926,7 +9946,7 @@
         <v>46395</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="35" t="n">
@@ -9944,7 +9964,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -9953,10 +9973,10 @@
         <v>158</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F29" s="31" t="s">
         <v>161</v>
@@ -9976,7 +9996,7 @@
         <v>46402</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="35" t="n">
@@ -9994,7 +10014,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -10003,10 +10023,10 @@
         <v>158</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F30" s="31" t="s">
         <v>168</v>
@@ -10026,7 +10046,7 @@
         <v>46402</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="35" t="n">
@@ -10044,19 +10064,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F31" s="31" t="s">
         <v>168</v>
@@ -10076,7 +10096,7 @@
         <v>46409</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="n">
@@ -10094,22 +10114,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G32" s="31" t="n">
         <v>8</v>
@@ -10126,7 +10146,7 @@
         <v>46409</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L32" s="34"/>
       <c r="M32" s="35" t="n">
@@ -10144,19 +10164,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F33" s="31" t="s">
         <v>161</v>
@@ -10176,7 +10196,7 @@
         <v>46409</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L33" s="34"/>
       <c r="M33" s="35" t="n">
@@ -10194,19 +10214,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F34" s="31" t="s">
         <v>161</v>
@@ -10226,7 +10246,7 @@
         <v>46416</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="35" t="n">
@@ -10244,19 +10264,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>161</v>
@@ -10276,7 +10296,7 @@
         <v>46416</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L35" s="34"/>
       <c r="M35" s="35" t="n">
@@ -10294,19 +10314,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F36" s="31" t="s">
         <v>161</v>
@@ -10326,7 +10346,7 @@
         <v>46423</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="n">
@@ -10344,19 +10364,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F37" s="31" t="s">
         <v>161</v>
@@ -10376,7 +10396,7 @@
         <v>46423</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="35" t="n">
@@ -10394,19 +10414,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F38" s="31" t="s">
         <v>161</v>
@@ -10426,7 +10446,7 @@
         <v>46423</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="n">
@@ -10444,19 +10464,19 @@
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F39" s="31" t="s">
         <v>168</v>
@@ -10476,7 +10496,7 @@
         <v>46423</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="35" t="n">
@@ -10494,19 +10514,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>168</v>
@@ -10526,7 +10546,7 @@
         <v>46423</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="35" t="n">
@@ -10584,7 +10604,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82A5B9AB-B140-4590-963F-50681642209C}</x14:id>
+          <x14:id>{8044D4CE-7F18-42E6-B1FE-16B071006042}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10615,7 +10635,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82A5B9AB-B140-4590-963F-50681642209C}">
+          <x14:cfRule type="dataBar" id="{8044D4CE-7F18-42E6-B1FE-16B071006042}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10662,34 +10682,34 @@
         <v>88</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10700,31 +10720,31 @@
         <v>96</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10735,31 +10755,31 @@
         <v>96</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10770,31 +10790,31 @@
         <v>96</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="J4" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="K4" s="31" t="s">
         <v>330</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10805,31 +10825,31 @@
         <v>96</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10840,31 +10860,31 @@
         <v>96</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10875,31 +10895,31 @@
         <v>96</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10910,31 +10930,31 @@
         <v>96</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10945,31 +10965,31 @@
         <v>96</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10980,31 +11000,31 @@
         <v>96</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11015,31 +11035,31 @@
         <v>96</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11050,31 +11070,31 @@
         <v>96</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11085,31 +11105,31 @@
         <v>96</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11117,34 +11137,34 @@
         <v>103</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11152,34 +11172,34 @@
         <v>104</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11187,34 +11207,34 @@
         <v>105</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11225,31 +11245,31 @@
         <v>96</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11257,34 +11277,34 @@
         <v>107</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11295,31 +11315,31 @@
         <v>96</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11330,31 +11350,31 @@
         <v>96</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11365,31 +11385,31 @@
         <v>96</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11400,31 +11420,31 @@
         <v>96</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11435,31 +11455,31 @@
         <v>96</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11467,34 +11487,34 @@
         <v>113</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11502,34 +11522,34 @@
         <v>114</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J25" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11537,34 +11557,34 @@
         <v>115</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J26" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11572,34 +11592,34 @@
         <v>116</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J27" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11607,34 +11627,34 @@
         <v>117</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J28" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11642,34 +11662,34 @@
         <v>118</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11677,34 +11697,34 @@
         <v>119</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11712,34 +11732,34 @@
         <v>120</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J31" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11747,34 +11767,34 @@
         <v>121</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I32" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J32" s="31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11782,34 +11802,34 @@
         <v>122</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J33" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11817,34 +11837,34 @@
         <v>123</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K34" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11852,34 +11872,34 @@
         <v>124</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K35" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11887,34 +11907,34 @@
         <v>125</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I36" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J36" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K36" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11922,34 +11942,34 @@
         <v>126</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I37" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11957,34 +11977,34 @@
         <v>127</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I38" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K38" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11992,34 +12012,34 @@
         <v>128</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K39" s="31" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12027,34 +12047,34 @@
         <v>129</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12062,34 +12082,34 @@
         <v>130</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I41" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12097,34 +12117,34 @@
         <v>131</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12132,34 +12152,34 @@
         <v>132</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J43" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12167,34 +12187,34 @@
         <v>133</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12202,34 +12222,34 @@
         <v>134</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J45" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K45" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12237,34 +12257,34 @@
         <v>135</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="K46" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12272,34 +12292,34 @@
         <v>136</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12310,31 +12330,31 @@
         <v>96</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I48" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -12389,7 +12409,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -12401,42 +12421,42 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -12449,40 +12469,40 @@
         <v>Grey</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>161</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46336</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -12498,31 +12518,37 @@
         <v>197</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I3" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="36"/>
-      <c r="M3" s="33"/>
+        <v>372</v>
+      </c>
+      <c r="L3" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>600</v>
+      </c>
       <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
+      <c r="O3" s="33" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -12535,22 +12561,22 @@
         <v>Black</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I4" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K4" s="33" t="s">
         <v>68</v>
@@ -12562,7 +12588,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
@@ -12575,22 +12601,22 @@
         <v>Black</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I5" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K5" s="33" t="s">
         <v>68</v>
@@ -12602,7 +12628,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
@@ -12615,22 +12641,22 @@
         <v>Black</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I6" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K6" s="33" t="s">
         <v>68</v>
@@ -12642,7 +12668,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
@@ -12655,22 +12681,22 @@
         <v>White</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I7" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K7" s="33" t="s">
         <v>68</v>
@@ -12682,7 +12708,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
@@ -12695,31 +12721,31 @@
         <v>White</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L8" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="N8" s="33"/>
       <c r="O8" s="33" t="s">
@@ -12728,7 +12754,7 @@
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -12741,40 +12767,40 @@
         <v>White</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L9" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
@@ -12787,22 +12813,22 @@
         <v>Black</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>68</v>
@@ -12814,7 +12840,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
@@ -12827,22 +12853,22 @@
         <v>Black</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>68</v>
@@ -12854,7 +12880,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -12867,22 +12893,22 @@
         <v>Grey</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>68</v>
@@ -12894,7 +12920,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
@@ -12907,22 +12933,22 @@
         <v>Grey</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I13" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>68</v>
@@ -12934,7 +12960,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
@@ -12947,22 +12973,22 @@
         <v>Grey</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="I14" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>68</v>
@@ -12974,7 +13000,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
@@ -12987,22 +13013,22 @@
         <v>White</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>68</v>
@@ -13014,7 +13040,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
@@ -13027,31 +13053,31 @@
         <v>White</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L16" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="N16" s="33"/>
       <c r="O16" s="33" t="s">
@@ -13060,7 +13086,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
@@ -13073,22 +13099,22 @@
         <v>Black</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="I17" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>68</v>
@@ -13100,7 +13126,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>5</v>
@@ -13113,22 +13139,22 @@
         <v>Grey</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I18" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>68</v>
@@ -13140,7 +13166,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>5</v>
@@ -13153,22 +13179,22 @@
         <v>Grey</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="I19" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>68</v>
@@ -13180,7 +13206,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>5</v>
@@ -13196,19 +13222,19 @@
         <v>5</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>68</v>
@@ -13220,7 +13246,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>5</v>
@@ -13233,22 +13259,22 @@
         <v>Black</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K21" s="33" t="s">
         <v>68</v>
@@ -13260,7 +13286,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -13273,22 +13299,22 @@
         <v>White</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>68</v>
@@ -13300,7 +13326,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -13313,22 +13339,22 @@
         <v>White</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I23" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>68</v>
@@ -13340,7 +13366,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -13353,22 +13379,22 @@
         <v>White</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="I24" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>68</v>
@@ -13380,7 +13406,7 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -13393,22 +13419,22 @@
         <v>Black</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I25" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K25" s="33" t="s">
         <v>68</v>
@@ -13420,7 +13446,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -13433,22 +13459,22 @@
         <v>Grey</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I26" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>68</v>
@@ -13460,7 +13486,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -13473,22 +13499,22 @@
         <v>White</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="I27" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K27" s="33" t="s">
         <v>68</v>
@@ -13500,7 +13526,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -13513,22 +13539,22 @@
         <v>Black</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I28" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K28" s="33" t="s">
         <v>68</v>
@@ -13540,7 +13566,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -13553,22 +13579,22 @@
         <v>Grey</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K29" s="33" t="s">
         <v>68</v>
@@ -13580,7 +13606,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -13593,22 +13619,22 @@
         <v>Black</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="I30" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K30" s="33" t="s">
         <v>68</v>
@@ -13620,7 +13646,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
@@ -13633,22 +13659,22 @@
         <v>Black</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I31" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K31" s="33" t="s">
         <v>68</v>
@@ -13660,7 +13686,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
@@ -13673,22 +13699,22 @@
         <v>White</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I32" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K32" s="33" t="s">
         <v>68</v>
@@ -13700,7 +13726,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
@@ -13713,22 +13739,22 @@
         <v>Black</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I33" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K33" s="33" t="s">
         <v>68</v>
@@ -13740,7 +13766,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
@@ -13753,22 +13779,22 @@
         <v>Grey</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I34" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K34" s="33" t="s">
         <v>68</v>
@@ -13780,7 +13806,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
@@ -13793,22 +13819,22 @@
         <v>Black</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I35" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K35" s="33" t="s">
         <v>68</v>
@@ -13820,7 +13846,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
@@ -13833,22 +13859,22 @@
         <v>Grey</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I36" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K36" s="33" t="s">
         <v>68</v>
@@ -13860,7 +13886,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -13873,22 +13899,22 @@
         <v>Black</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I37" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K37" s="33" t="s">
         <v>68</v>
@@ -13900,7 +13926,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
@@ -13913,22 +13939,22 @@
         <v>Grey</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="I38" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K38" s="33" t="s">
         <v>68</v>
@@ -13940,7 +13966,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
@@ -13953,22 +13979,22 @@
         <v>Black</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I39" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K39" s="33" t="s">
         <v>68</v>
@@ -13980,7 +14006,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
@@ -13993,22 +14019,22 @@
         <v>Black</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K40" s="33" t="s">
         <v>68</v>
@@ -14020,7 +14046,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>7</v>
@@ -14033,22 +14059,22 @@
         <v>Black</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="I41" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K41" s="33" t="s">
         <v>68</v>
@@ -14060,7 +14086,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>7</v>
@@ -14073,22 +14099,22 @@
         <v>Black</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I42" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K42" s="33" t="s">
         <v>68</v>
@@ -14100,7 +14126,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>7</v>
@@ -14113,22 +14139,22 @@
         <v>Black</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I43" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K43" s="33" t="s">
         <v>68</v>
@@ -14140,7 +14166,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>7</v>
@@ -14153,22 +14179,22 @@
         <v>Black</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I44" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K44" s="33" t="s">
         <v>68</v>
@@ -14180,7 +14206,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
@@ -14193,22 +14219,22 @@
         <v>Black</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I45" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K45" s="33" t="s">
         <v>68</v>
@@ -14220,7 +14246,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>7</v>
@@ -14233,22 +14259,22 @@
         <v>Black</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I46" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K46" s="33" t="s">
         <v>68</v>
@@ -14260,7 +14286,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>7</v>
@@ -14273,22 +14299,22 @@
         <v>Black</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="I47" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K47" s="33" t="s">
         <v>68</v>
@@ -14365,43 +14391,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>155</v>
@@ -14409,7 +14435,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -14418,16 +14444,16 @@
         <v>42</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F2" s="37" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="H2" s="37" t="n">
         <v>38</v>
@@ -14437,40 +14463,40 @@
         <v>PASS</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46338</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="N2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F3" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H3" s="39"/>
       <c r="I3" s="31" t="str">
@@ -14478,7 +14504,7 @@
         <v>PENDING</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
@@ -14487,7 +14513,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -14496,16 +14522,16 @@
         <v>42</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F4" s="40" t="n">
         <v>300</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="31" t="str">
@@ -14513,7 +14539,7 @@
         <v>PENDING</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="36"/>
@@ -14522,25 +14548,25 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F5" s="40" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H5" s="41" t="n">
         <v>3.3</v>
@@ -14550,42 +14576,42 @@
         <v>PASS</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F6" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="31" t="str">
@@ -14593,7 +14619,7 @@
         <v>PENDING</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="36"/>
@@ -14602,25 +14628,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H7" s="39"/>
       <c r="I7" s="31" t="str">
@@ -14628,7 +14654,7 @@
         <v>PENDING</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
@@ -14637,25 +14663,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="31" t="str">
@@ -14663,7 +14689,7 @@
         <v>PENDING</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="36"/>
@@ -14672,25 +14698,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="H9" s="41"/>
       <c r="I9" s="31" t="str">
@@ -14698,7 +14724,7 @@
         <v>PENDING</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
@@ -14707,25 +14733,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="31" t="str">
@@ -14733,7 +14759,7 @@
         <v>PENDING</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="36"/>
@@ -14742,25 +14768,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="31" t="str">
@@ -14768,7 +14794,7 @@
         <v>PENDING</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="36"/>
@@ -14777,25 +14803,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F12" s="40" t="n">
         <v>10000</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="31" t="str">
@@ -14803,7 +14829,7 @@
         <v>PENDING</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K12" s="33"/>
       <c r="L12" s="36"/>
@@ -14812,7 +14838,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>7</v>
@@ -14821,16 +14847,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F13" s="40" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="31" t="str">
@@ -14838,7 +14864,7 @@
         <v>PENDING</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="36"/>
@@ -14847,7 +14873,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>7</v>
@@ -14856,16 +14882,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="31" t="str">
@@ -14873,7 +14899,7 @@
         <v>PENDING</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="36"/>
@@ -14882,25 +14908,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>0.001</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="31" t="str">
@@ -14908,7 +14934,7 @@
         <v>PENDING</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K15" s="33"/>
       <c r="L15" s="36"/>
@@ -14917,25 +14943,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="31" t="str">
@@ -14943,7 +14969,7 @@
         <v>PENDING</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="36"/>
@@ -14952,25 +14978,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="31" t="str">
@@ -14978,7 +15004,7 @@
         <v>PENDING</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="36"/>
@@ -14987,25 +15013,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="31" t="str">
@@ -15013,7 +15039,7 @@
         <v>PENDING</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="36"/>
@@ -15022,7 +15048,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -15031,16 +15057,16 @@
         <v>42</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="31" t="str">
@@ -15048,7 +15074,7 @@
         <v>PENDING</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="36"/>
@@ -15057,25 +15083,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>15</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="31" t="str">
@@ -15083,7 +15109,7 @@
         <v>PENDING</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
@@ -15092,25 +15118,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="31" t="str">
@@ -15118,7 +15144,7 @@
         <v>PENDING</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="36"/>
@@ -15127,25 +15153,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0.75</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="31" t="str">
@@ -15153,7 +15179,7 @@
         <v>PENDING</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="36"/>
@@ -15162,25 +15188,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>0.9995</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H23" s="39"/>
       <c r="I23" s="31" t="str">
@@ -15188,7 +15214,7 @@
         <v>PENDING</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="36"/>
@@ -15259,7 +15285,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -15268,69 +15294,69 @@
         <v>88</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -15339,13 +15365,13 @@
         <v>114</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G2" s="28" t="n">
         <v>30</v>
@@ -15395,15 +15421,15 @@
         <v>46338</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -15412,13 +15438,13 @@
         <v>114</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>15</v>
@@ -15454,7 +15480,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -15463,13 +15489,13 @@
         <v>116</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G4" s="31" t="n">
         <v>5</v>
@@ -15505,7 +15531,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
@@ -15514,13 +15540,13 @@
         <v>114</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>30</v>
@@ -15556,7 +15582,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
@@ -15565,13 +15591,13 @@
         <v>115</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>30</v>
@@ -15607,7 +15633,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
@@ -15616,13 +15642,13 @@
         <v>116</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>5</v>
@@ -15658,7 +15684,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
@@ -15667,13 +15693,13 @@
         <v>117</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>480</v>
@@ -15709,7 +15735,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -15718,13 +15744,13 @@
         <v>118</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G9" s="31" t="n">
         <v>30</v>
@@ -15760,7 +15786,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>7</v>
@@ -15769,13 +15795,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G10" s="31" t="n">
         <v>15</v>
@@ -15862,72 +15888,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="I2" s="28" t="n">
         <v>12</v>
@@ -15936,7 +15962,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46340</v>
@@ -15946,30 +15972,30 @@
         <v>PASS</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
@@ -15986,25 +16012,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
@@ -16021,25 +16047,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
@@ -16056,25 +16082,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
@@ -16091,25 +16117,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -16126,25 +16152,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
@@ -16161,25 +16187,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -16252,40 +16278,40 @@
         <v>140</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16293,13 +16319,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E2" s="30" t="n">
         <v>0.93</v>
@@ -16327,7 +16353,7 @@
         <v>46346</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16335,13 +16361,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
@@ -16367,13 +16393,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>968</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>964</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>960</v>
-      </c>
       <c r="D4" s="31" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -16399,13 +16425,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -16431,13 +16457,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
+        <v>969</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>964</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>965</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>960</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>961</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -16463,13 +16489,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16495,13 +16521,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="998">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -783,21 +783,27 @@
     <t xml:space="preserve">Cross-tenant access test fails closed</t>
   </si>
   <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40079839501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoD: cross-tenant access fails closed, in CI on every identity change (RowLevelSecurityTest, ProjectApiTest) and on RDS through EKS (run 40079839501: 83/83 checks, 107 resources applied and destroyed). With no tenant scope, identity_dev sees 0 tenants on RDS right after one was created, and its inserts are refused. Built: ADR-0009; tenant &gt; project &gt; environment (new projects get production/live and sandbox/test; limits 100/20; per-tenant slugs); FORCE row-level security on every tenant table, keyed on a transaction-local app.tenant_id via TenantScope, plus a narrow logged platform scope; a guard test fails the build if a table skips RLS; tests run as a NOSUPERUSER NOBYPASSRLS role; /v1/projects API with two isolation layers; 176 tests (97.4% line / 87.0% branch). Found and fixed: scope restore masking the original DB error; reserved connection slots under a non-superuser; duplicated kubectl output failing correct EKS checks. Evidence: docs/evidence/2026-10-24-tenancy-row-level-security.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB-T09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoped, hashed API keys with rotation and revocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revoked key rejected within 60 s</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Started</t>
   </si>
   <si>
-    <t xml:space="preserve">MB-T09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scoped, hashed API keys with rotation and revocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revoked key rejected within 60 s</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB-T10</t>
   </si>
   <si>
@@ -1978,6 +1984,9 @@
   </si>
   <si>
     <t xml:space="preserve">403/404; RLS blocks query; audit event logged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolation parts pass: tenant B gets 404 on every A project/environment route and its writes change nothing; RLS returns 0 rows and refuses writes with no scope, in CI and on RDS. Audit event not yet built (MB-T11), so the case stays Blocked until then.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-003</t>
@@ -4248,60 +4257,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4314,13 +4323,13 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6074,34 +6083,34 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6179,7 +6188,7 @@
       </c>
       <c r="E4" s="31" t="n">
         <f aca="false">COUNTIFS(Plan!$H$2:$H$600,A4,Plan!$K$2:$K$600,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="31" t="n">
         <f aca="false">SUMIF(Plan!$H$2:$H$600,A4,Plan!$G$2:$G$600)</f>
@@ -6601,7 +6610,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,B$4,Plan!$K$2:$K$600,"Done")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,C$4,Plan!$K$2:$K$600,"Done")</f>
@@ -6609,7 +6618,7 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">SUM(B8:C8)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6686,7 +6695,7 @@
       </c>
       <c r="B13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=B$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=C$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
@@ -6694,7 +6703,7 @@
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">SUM(B13:C13)</f>
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6703,7 +6712,7 @@
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">IFERROR(B13/B12,0)</f>
-        <v>0.506666666666667</v>
+        <v>0.586666666666667</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C13/C12,0)</f>
@@ -6711,7 +6720,7 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">IFERROR(D13/D12,0)</f>
-        <v>0.176744186046512</v>
+        <v>0.204651162790698</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6779,7 +6788,7 @@
       </c>
       <c r="B20" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Blocked")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Blocked")</f>
@@ -6787,7 +6796,7 @@
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">SUM(B20:C20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6796,7 +6805,7 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
@@ -6804,7 +6813,7 @@
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">SUM(B21:C21)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6813,7 +6822,7 @@
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IFERROR((B17-B21)/B17,0)</f>
-        <v>0.210526315789474</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">IFERROR((C17-C21)/C17,0)</f>
@@ -6821,7 +6830,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">IFERROR((D17-D21)/D17,0)</f>
-        <v>0.0888888888888889</v>
+        <v>0.111111111111111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8133,7 +8142,7 @@
       </c>
       <c r="F86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Not Run")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Not Run",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8312,7 +8321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B9133E3B-DA92-4DCB-9CEB-40B43A3957E8}</x14:id>
+          <x14:id>{628D9AFD-2A27-48F9-82A7-3094233FDB95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8326,7 +8335,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CD282A99-D9C3-4DD6-9C2B-29781978C26C}</x14:id>
+          <x14:id>{1D7B3917-18F6-4CDC-8540-431268157140}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8340,7 +8349,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B013A9A5-C4CC-48C7-A022-F3FDC164D331}</x14:id>
+          <x14:id>{6EE7B192-71F5-41DF-A982-A0FE7C137657}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8354,7 +8363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A2CFB084-B488-4DA7-9E76-7CA95595B5AE}</x14:id>
+          <x14:id>{401810BF-4692-422B-B4B2-6D3EAAF5E42A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8400,7 +8409,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B9133E3B-DA92-4DCB-9CEB-40B43A3957E8}">
+          <x14:cfRule type="dataBar" id="{628D9AFD-2A27-48F9-82A7-3094233FDB95}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8415,7 +8424,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CD282A99-D9C3-4DD6-9C2B-29781978C26C}">
+          <x14:cfRule type="dataBar" id="{1D7B3917-18F6-4CDC-8540-431268157140}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8430,7 +8439,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B013A9A5-C4CC-48C7-A022-F3FDC164D331}">
+          <x14:cfRule type="dataBar" id="{6EE7B192-71F5-41DF-A982-A0FE7C137657}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8445,7 +8454,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A2CFB084-B488-4DA7-9E76-7CA95595B5AE}">
+          <x14:cfRule type="dataBar" id="{401810BF-4692-422B-B4B2-6D3EAAF5E42A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -9046,37 +9055,45 @@
         <v>46346</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="L10" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="L10" s="34" t="n">
+        <v>1</v>
+      </c>
       <c r="M10" s="35" t="n">
         <f aca="false">IF(K10="Done",1,IF(L10="",0,MIN(1,L10)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="33"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="36" t="n">
+        <v>46319</v>
+      </c>
       <c r="P10" s="31" t="str">
         <f aca="true">IF(K10="Done",IF(O10="","Done",IF(J10="","Done",IF(O10&lt;=J10,"On time","Late"))),IF(K10="Blocked","BLOCKED",IF(I10="","",IF(TODAY()&gt;J10,"OVERDUE",IF(TODAY()&gt;=I10,"Active","Upcoming")))))</f>
-        <v>Upcoming</v>
-      </c>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
+        <v>On time</v>
+      </c>
+      <c r="Q10" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="R10" s="33" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F11" s="31" t="s">
         <v>161</v>
@@ -9096,7 +9113,7 @@
         <v>46346</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="35" t="n">
@@ -9114,19 +9131,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F12" s="31" t="s">
         <v>168</v>
@@ -9146,7 +9163,7 @@
         <v>46353</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35" t="n">
@@ -9164,19 +9181,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>161</v>
@@ -9196,7 +9213,7 @@
         <v>46353</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="n">
@@ -9214,19 +9231,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F14" s="31" t="s">
         <v>161</v>
@@ -9246,7 +9263,7 @@
         <v>46353</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="n">
@@ -9264,19 +9281,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F15" s="31" t="s">
         <v>168</v>
@@ -9296,7 +9313,7 @@
         <v>46353</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="n">
@@ -9314,19 +9331,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F16" s="31" t="s">
         <v>161</v>
@@ -9346,7 +9363,7 @@
         <v>46353</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="n">
@@ -9364,22 +9381,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G17" s="31" t="n">
         <v>4</v>
@@ -9396,7 +9413,7 @@
         <v>46353</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35" t="n">
@@ -9414,7 +9431,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
@@ -9423,10 +9440,10 @@
         <v>165</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F18" s="31" t="s">
         <v>161</v>
@@ -9446,7 +9463,7 @@
         <v>46360</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="n">
@@ -9464,7 +9481,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -9473,10 +9490,10 @@
         <v>165</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F19" s="31" t="s">
         <v>161</v>
@@ -9496,7 +9513,7 @@
         <v>46360</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="n">
@@ -9514,7 +9531,7 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
@@ -9523,10 +9540,10 @@
         <v>165</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F20" s="31" t="s">
         <v>161</v>
@@ -9546,7 +9563,7 @@
         <v>46360</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="n">
@@ -9564,7 +9581,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
@@ -9573,10 +9590,10 @@
         <v>158</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F21" s="31" t="s">
         <v>161</v>
@@ -9596,7 +9613,7 @@
         <v>46367</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="n">
@@ -9614,7 +9631,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -9623,10 +9640,10 @@
         <v>158</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F22" s="31" t="s">
         <v>161</v>
@@ -9646,7 +9663,7 @@
         <v>46367</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="n">
@@ -9664,7 +9681,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -9673,10 +9690,10 @@
         <v>158</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>161</v>
@@ -9696,7 +9713,7 @@
         <v>46374</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="n">
@@ -9714,7 +9731,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -9723,10 +9740,10 @@
         <v>158</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F24" s="31" t="s">
         <v>161</v>
@@ -9746,7 +9763,7 @@
         <v>46381</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="n">
@@ -9764,7 +9781,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -9773,10 +9790,10 @@
         <v>158</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F25" s="31" t="s">
         <v>161</v>
@@ -9796,7 +9813,7 @@
         <v>46388</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="n">
@@ -9814,7 +9831,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -9823,10 +9840,10 @@
         <v>158</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F26" s="31" t="s">
         <v>161</v>
@@ -9846,7 +9863,7 @@
         <v>46388</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="n">
@@ -9864,7 +9881,7 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -9873,10 +9890,10 @@
         <v>158</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>161</v>
@@ -9896,7 +9913,7 @@
         <v>46395</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35" t="n">
@@ -9914,7 +9931,7 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -9923,10 +9940,10 @@
         <v>158</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F28" s="31" t="s">
         <v>168</v>
@@ -9946,7 +9963,7 @@
         <v>46395</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="35" t="n">
@@ -9964,7 +9981,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -9973,10 +9990,10 @@
         <v>158</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F29" s="31" t="s">
         <v>161</v>
@@ -9996,7 +10013,7 @@
         <v>46402</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="35" t="n">
@@ -10014,7 +10031,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -10023,10 +10040,10 @@
         <v>158</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F30" s="31" t="s">
         <v>168</v>
@@ -10046,7 +10063,7 @@
         <v>46402</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="35" t="n">
@@ -10064,19 +10081,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F31" s="31" t="s">
         <v>168</v>
@@ -10096,7 +10113,7 @@
         <v>46409</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="n">
@@ -10114,22 +10131,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G32" s="31" t="n">
         <v>8</v>
@@ -10146,7 +10163,7 @@
         <v>46409</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L32" s="34"/>
       <c r="M32" s="35" t="n">
@@ -10164,19 +10181,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F33" s="31" t="s">
         <v>161</v>
@@ -10196,7 +10213,7 @@
         <v>46409</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L33" s="34"/>
       <c r="M33" s="35" t="n">
@@ -10214,19 +10231,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F34" s="31" t="s">
         <v>161</v>
@@ -10246,7 +10263,7 @@
         <v>46416</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="35" t="n">
@@ -10264,19 +10281,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>161</v>
@@ -10296,7 +10313,7 @@
         <v>46416</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L35" s="34"/>
       <c r="M35" s="35" t="n">
@@ -10314,19 +10331,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F36" s="31" t="s">
         <v>161</v>
@@ -10346,7 +10363,7 @@
         <v>46423</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="n">
@@ -10364,19 +10381,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F37" s="31" t="s">
         <v>161</v>
@@ -10396,7 +10413,7 @@
         <v>46423</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="35" t="n">
@@ -10414,19 +10431,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F38" s="31" t="s">
         <v>161</v>
@@ -10446,7 +10463,7 @@
         <v>46423</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="n">
@@ -10464,19 +10481,19 @@
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F39" s="31" t="s">
         <v>168</v>
@@ -10496,7 +10513,7 @@
         <v>46423</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="35" t="n">
@@ -10514,19 +10531,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>168</v>
@@ -10546,7 +10563,7 @@
         <v>46423</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="35" t="n">
@@ -10604,7 +10621,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8044D4CE-7F18-42E6-B1FE-16B071006042}</x14:id>
+          <x14:id>{2873B13A-6276-4CDE-AFC8-DCC4F9F58045}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10635,7 +10652,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8044D4CE-7F18-42E6-B1FE-16B071006042}">
+          <x14:cfRule type="dataBar" id="{2873B13A-6276-4CDE-AFC8-DCC4F9F58045}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10682,34 +10699,34 @@
         <v>88</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10720,31 +10737,31 @@
         <v>96</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10755,31 +10772,31 @@
         <v>96</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10790,31 +10807,31 @@
         <v>96</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="J4" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="K4" s="31" t="s">
         <v>332</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10825,31 +10842,31 @@
         <v>96</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10860,31 +10877,31 @@
         <v>96</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10895,31 +10912,31 @@
         <v>96</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10930,31 +10947,31 @@
         <v>96</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10965,31 +10982,31 @@
         <v>96</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11000,31 +11017,31 @@
         <v>96</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11035,31 +11052,31 @@
         <v>96</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11070,31 +11087,31 @@
         <v>96</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11105,31 +11122,31 @@
         <v>96</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11137,34 +11154,34 @@
         <v>103</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11172,34 +11189,34 @@
         <v>104</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11207,34 +11224,34 @@
         <v>105</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11245,31 +11262,31 @@
         <v>96</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11277,34 +11294,34 @@
         <v>107</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11315,31 +11332,31 @@
         <v>96</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11350,31 +11367,31 @@
         <v>96</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11385,31 +11402,31 @@
         <v>96</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11420,31 +11437,31 @@
         <v>96</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11455,31 +11472,31 @@
         <v>96</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11487,34 +11504,34 @@
         <v>113</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11522,34 +11539,34 @@
         <v>114</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J25" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11557,34 +11574,34 @@
         <v>115</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J26" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11592,34 +11609,34 @@
         <v>116</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J27" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11627,34 +11644,34 @@
         <v>117</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J28" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11662,34 +11679,34 @@
         <v>118</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11697,34 +11714,34 @@
         <v>119</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11732,34 +11749,34 @@
         <v>120</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J31" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11767,34 +11784,34 @@
         <v>121</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J32" s="31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11802,34 +11819,34 @@
         <v>122</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J33" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11837,34 +11854,34 @@
         <v>123</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K34" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11872,34 +11889,34 @@
         <v>124</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K35" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11907,34 +11924,34 @@
         <v>125</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I36" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J36" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K36" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11942,34 +11959,34 @@
         <v>126</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I37" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11977,34 +11994,34 @@
         <v>127</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I38" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K38" s="31" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12012,34 +12029,34 @@
         <v>128</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="K39" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12047,34 +12064,34 @@
         <v>129</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12082,34 +12099,34 @@
         <v>130</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12117,34 +12134,34 @@
         <v>131</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12152,34 +12169,34 @@
         <v>132</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J43" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12187,34 +12204,34 @@
         <v>133</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12222,34 +12239,34 @@
         <v>134</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J45" s="31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="K45" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12257,34 +12274,34 @@
         <v>135</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K46" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12292,34 +12309,34 @@
         <v>136</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12330,31 +12347,31 @@
         <v>96</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I48" s="31" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -12409,7 +12426,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -12421,42 +12438,42 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -12469,40 +12486,40 @@
         <v>Grey</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>161</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46336</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="28" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -12518,37 +12535,37 @@
         <v>197</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="I3" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L3" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N3" s="33"/>
       <c r="O3" s="33" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -12564,31 +12581,37 @@
         <v>203</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I4" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="36"/>
-      <c r="M4" s="33"/>
+        <v>59</v>
+      </c>
+      <c r="L4" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>607</v>
+      </c>
       <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
+      <c r="O4" s="33" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
@@ -12601,22 +12624,22 @@
         <v>Black</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I5" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K5" s="33" t="s">
         <v>68</v>
@@ -12628,7 +12651,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
@@ -12641,22 +12664,22 @@
         <v>Black</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I6" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K6" s="33" t="s">
         <v>68</v>
@@ -12668,7 +12691,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
@@ -12681,22 +12704,22 @@
         <v>White</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I7" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K7" s="33" t="s">
         <v>68</v>
@@ -12708,7 +12731,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
@@ -12721,31 +12744,31 @@
         <v>White</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L8" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N8" s="33"/>
       <c r="O8" s="33" t="s">
@@ -12754,7 +12777,7 @@
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -12767,40 +12790,40 @@
         <v>White</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L9" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
@@ -12813,22 +12836,22 @@
         <v>Black</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>68</v>
@@ -12840,7 +12863,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
@@ -12853,22 +12876,22 @@
         <v>Black</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>68</v>
@@ -12880,7 +12903,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -12893,22 +12916,22 @@
         <v>Grey</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>68</v>
@@ -12920,7 +12943,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
@@ -12933,22 +12956,22 @@
         <v>Grey</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I13" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>68</v>
@@ -12960,7 +12983,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
@@ -12973,22 +12996,22 @@
         <v>Grey</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="I14" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>68</v>
@@ -13000,7 +13023,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
@@ -13013,22 +13036,22 @@
         <v>White</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>68</v>
@@ -13040,7 +13063,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
@@ -13053,31 +13076,31 @@
         <v>White</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L16" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="N16" s="33"/>
       <c r="O16" s="33" t="s">
@@ -13086,7 +13109,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
@@ -13099,22 +13122,22 @@
         <v>Black</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="I17" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>68</v>
@@ -13126,7 +13149,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>5</v>
@@ -13139,22 +13162,22 @@
         <v>Grey</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I18" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>68</v>
@@ -13166,7 +13189,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>5</v>
@@ -13179,22 +13202,22 @@
         <v>Grey</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="I19" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>68</v>
@@ -13206,7 +13229,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>5</v>
@@ -13222,19 +13245,19 @@
         <v>5</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>68</v>
@@ -13246,7 +13269,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>5</v>
@@ -13259,22 +13282,22 @@
         <v>Black</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K21" s="33" t="s">
         <v>68</v>
@@ -13286,7 +13309,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -13299,22 +13322,22 @@
         <v>White</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>68</v>
@@ -13326,7 +13349,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -13339,22 +13362,22 @@
         <v>White</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I23" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>68</v>
@@ -13366,7 +13389,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -13379,22 +13402,22 @@
         <v>White</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="I24" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>68</v>
@@ -13406,7 +13429,7 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -13419,22 +13442,22 @@
         <v>Black</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I25" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K25" s="33" t="s">
         <v>68</v>
@@ -13446,7 +13469,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -13459,22 +13482,22 @@
         <v>Grey</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I26" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>68</v>
@@ -13486,7 +13509,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -13499,22 +13522,22 @@
         <v>White</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="I27" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K27" s="33" t="s">
         <v>68</v>
@@ -13526,7 +13549,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -13539,22 +13562,22 @@
         <v>Black</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I28" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K28" s="33" t="s">
         <v>68</v>
@@ -13566,7 +13589,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -13579,22 +13602,22 @@
         <v>Grey</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K29" s="33" t="s">
         <v>68</v>
@@ -13606,7 +13629,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -13619,22 +13642,22 @@
         <v>Black</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="I30" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K30" s="33" t="s">
         <v>68</v>
@@ -13646,7 +13669,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
@@ -13659,22 +13682,22 @@
         <v>Black</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I31" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K31" s="33" t="s">
         <v>68</v>
@@ -13686,7 +13709,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
@@ -13699,22 +13722,22 @@
         <v>White</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I32" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K32" s="33" t="s">
         <v>68</v>
@@ -13726,7 +13749,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
@@ -13739,22 +13762,22 @@
         <v>Black</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I33" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K33" s="33" t="s">
         <v>68</v>
@@ -13766,7 +13789,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
@@ -13779,22 +13802,22 @@
         <v>Grey</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="I34" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K34" s="33" t="s">
         <v>68</v>
@@ -13806,7 +13829,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
@@ -13819,22 +13842,22 @@
         <v>Black</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I35" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K35" s="33" t="s">
         <v>68</v>
@@ -13846,7 +13869,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
@@ -13859,22 +13882,22 @@
         <v>Grey</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I36" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K36" s="33" t="s">
         <v>68</v>
@@ -13886,7 +13909,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -13899,22 +13922,22 @@
         <v>Black</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I37" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K37" s="33" t="s">
         <v>68</v>
@@ -13926,7 +13949,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
@@ -13939,22 +13962,22 @@
         <v>Grey</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="I38" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K38" s="33" t="s">
         <v>68</v>
@@ -13966,7 +13989,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
@@ -13979,22 +14002,22 @@
         <v>Black</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I39" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K39" s="33" t="s">
         <v>68</v>
@@ -14006,7 +14029,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
@@ -14019,22 +14042,22 @@
         <v>Black</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K40" s="33" t="s">
         <v>68</v>
@@ -14046,7 +14069,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>7</v>
@@ -14059,22 +14082,22 @@
         <v>Black</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="I41" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K41" s="33" t="s">
         <v>68</v>
@@ -14086,7 +14109,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>7</v>
@@ -14099,22 +14122,22 @@
         <v>Black</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I42" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K42" s="33" t="s">
         <v>68</v>
@@ -14126,7 +14149,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>7</v>
@@ -14139,22 +14162,22 @@
         <v>Black</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I43" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K43" s="33" t="s">
         <v>68</v>
@@ -14166,7 +14189,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>7</v>
@@ -14179,22 +14202,22 @@
         <v>Black</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I44" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K44" s="33" t="s">
         <v>68</v>
@@ -14206,7 +14229,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
@@ -14219,22 +14242,22 @@
         <v>Black</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I45" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K45" s="33" t="s">
         <v>68</v>
@@ -14246,7 +14269,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>7</v>
@@ -14259,22 +14282,22 @@
         <v>Black</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I46" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K46" s="33" t="s">
         <v>68</v>
@@ -14286,7 +14309,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>7</v>
@@ -14299,22 +14322,22 @@
         <v>Black</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="I47" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K47" s="33" t="s">
         <v>68</v>
@@ -14391,43 +14414,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>155</v>
@@ -14435,7 +14458,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -14444,16 +14467,16 @@
         <v>42</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F2" s="37" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H2" s="37" t="n">
         <v>38</v>
@@ -14463,40 +14486,40 @@
         <v>PASS</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46338</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="N2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F3" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H3" s="39"/>
       <c r="I3" s="31" t="str">
@@ -14504,7 +14527,7 @@
         <v>PENDING</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
@@ -14513,7 +14536,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -14522,16 +14545,16 @@
         <v>42</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F4" s="40" t="n">
         <v>300</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="31" t="str">
@@ -14539,7 +14562,7 @@
         <v>PENDING</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="36"/>
@@ -14548,25 +14571,25 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F5" s="40" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H5" s="41" t="n">
         <v>3.3</v>
@@ -14576,42 +14599,42 @@
         <v>PASS</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F6" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="31" t="str">
@@ -14619,7 +14642,7 @@
         <v>PENDING</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="36"/>
@@ -14628,25 +14651,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H7" s="39"/>
       <c r="I7" s="31" t="str">
@@ -14654,7 +14677,7 @@
         <v>PENDING</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
@@ -14663,25 +14686,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="31" t="str">
@@ -14689,7 +14712,7 @@
         <v>PENDING</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="36"/>
@@ -14698,25 +14721,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="H9" s="41"/>
       <c r="I9" s="31" t="str">
@@ -14724,7 +14747,7 @@
         <v>PENDING</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
@@ -14733,25 +14756,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="31" t="str">
@@ -14759,7 +14782,7 @@
         <v>PENDING</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="36"/>
@@ -14768,25 +14791,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="31" t="str">
@@ -14794,7 +14817,7 @@
         <v>PENDING</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="36"/>
@@ -14803,25 +14826,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F12" s="40" t="n">
         <v>10000</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="31" t="str">
@@ -14829,7 +14852,7 @@
         <v>PENDING</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K12" s="33"/>
       <c r="L12" s="36"/>
@@ -14838,7 +14861,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>7</v>
@@ -14847,16 +14870,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F13" s="40" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="31" t="str">
@@ -14864,7 +14887,7 @@
         <v>PENDING</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="36"/>
@@ -14873,7 +14896,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>7</v>
@@ -14882,16 +14905,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="31" t="str">
@@ -14899,7 +14922,7 @@
         <v>PENDING</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="36"/>
@@ -14908,25 +14931,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>0.001</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="31" t="str">
@@ -14934,7 +14957,7 @@
         <v>PENDING</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K15" s="33"/>
       <c r="L15" s="36"/>
@@ -14943,25 +14966,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="31" t="str">
@@ -14969,7 +14992,7 @@
         <v>PENDING</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="36"/>
@@ -14978,25 +15001,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="31" t="str">
@@ -15004,7 +15027,7 @@
         <v>PENDING</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="36"/>
@@ -15013,25 +15036,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="31" t="str">
@@ -15039,7 +15062,7 @@
         <v>PENDING</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="36"/>
@@ -15048,7 +15071,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -15057,16 +15080,16 @@
         <v>42</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="31" t="str">
@@ -15074,7 +15097,7 @@
         <v>PENDING</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="36"/>
@@ -15083,25 +15106,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>15</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="31" t="str">
@@ -15109,7 +15132,7 @@
         <v>PENDING</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
@@ -15118,25 +15141,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="31" t="str">
@@ -15144,7 +15167,7 @@
         <v>PENDING</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="36"/>
@@ -15153,25 +15176,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0.75</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="31" t="str">
@@ -15179,7 +15202,7 @@
         <v>PENDING</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="36"/>
@@ -15188,25 +15211,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>0.9995</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H23" s="39"/>
       <c r="I23" s="31" t="str">
@@ -15214,7 +15237,7 @@
         <v>PENDING</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="36"/>
@@ -15285,7 +15308,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -15294,69 +15317,69 @@
         <v>88</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -15365,13 +15388,13 @@
         <v>114</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G2" s="28" t="n">
         <v>30</v>
@@ -15421,15 +15444,15 @@
         <v>46338</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -15438,13 +15461,13 @@
         <v>114</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>15</v>
@@ -15480,7 +15503,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -15489,13 +15512,13 @@
         <v>116</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G4" s="31" t="n">
         <v>5</v>
@@ -15531,7 +15554,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
@@ -15540,13 +15563,13 @@
         <v>114</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>30</v>
@@ -15582,7 +15605,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
@@ -15591,13 +15614,13 @@
         <v>115</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>30</v>
@@ -15633,7 +15656,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
@@ -15642,13 +15665,13 @@
         <v>116</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>5</v>
@@ -15684,7 +15707,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
@@ -15693,13 +15716,13 @@
         <v>117</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>480</v>
@@ -15735,7 +15758,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -15744,13 +15767,13 @@
         <v>118</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G9" s="31" t="n">
         <v>30</v>
@@ -15786,7 +15809,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>7</v>
@@ -15795,13 +15818,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="G10" s="31" t="n">
         <v>15</v>
@@ -15888,72 +15911,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>785</v>
       </c>
-      <c r="M1" s="13" t="s">
-        <v>782</v>
-      </c>
       <c r="N1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="I2" s="28" t="n">
         <v>12</v>
@@ -15962,7 +15985,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46340</v>
@@ -15972,30 +15995,30 @@
         <v>PASS</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
@@ -16012,25 +16035,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
@@ -16047,25 +16070,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
@@ -16082,25 +16105,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
@@ -16117,25 +16140,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -16152,25 +16175,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
@@ -16187,25 +16210,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -16278,40 +16301,40 @@
         <v>140</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16319,13 +16342,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E2" s="30" t="n">
         <v>0.93</v>
@@ -16353,7 +16376,7 @@
         <v>46346</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16361,13 +16384,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="31" t="s">
+        <v>970</v>
+      </c>
+      <c r="C3" s="31" t="s">
         <v>967</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>964</v>
-      </c>
       <c r="D3" s="31" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
@@ -16393,13 +16416,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>967</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>968</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>964</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>965</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -16425,13 +16448,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -16457,13 +16480,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -16489,13 +16512,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16521,13 +16544,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="1002">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -801,18 +801,24 @@
     <t xml:space="preserve">Revoked key rejected within 60 s</t>
   </si>
   <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40085243536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoD: a revoked key is rejected on the very next request by identity (API test and browser e2e with a real Keycloak tenant admin, CI run 40084140187); other services may cache a verification for at most 30 s (Cache-Control: max-age=30; refusals no-store), so every service rejects it within 30 s. On EKS (run 40085243536): 87/87 checks, 107 resources applied and destroyed; /v1/api-key refuses no credentials, unknown keys and access tokens with no-store; V6 on RDS under forced RLS. Built: ADR-0010; keys mb_live_/mb_test_ + 238 random bits + CRC-32, SHA-256 at rest, shown once, never in idempotency records; one environment per key; scopes from a fixed vocabulary; expiry; rotation with a grace period; immediate revocation; 50 live keys per environment; last_used_at; keys cannot call the admin API. 193 tests (97.5% line / 87.1% branch). Found and fixed: timestamps serialised in the JVM zone instead of UTC; 500 for a non-key authentication on /v1/api-key; expired keys counting toward the limit; jOOQ self-reference clash. Evidence: docs/evidence/2026-10-24-api-keys.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB-T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service mesh mTLS (Linkerd or Istio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaintext pod-to-pod traffic rejected</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Started</t>
   </si>
   <si>
-    <t xml:space="preserve">MB-T10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service mesh mTLS (Linkerd or Istio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaintext pod-to-pod traffic rejected</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB-T11</t>
   </si>
   <si>
@@ -1999,6 +2005,12 @@
   </si>
   <si>
     <t xml:space="preserve">401 within 60 s of revocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401 on the very next request after revocation, in the API test and in the browser e2e with a real Keycloak tenant admin; callers cache at most 30 s (max-age=30), refusals are no-store; EKS checks pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40084140187</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-004</t>
@@ -4257,60 +4269,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4323,13 +4335,13 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6083,34 +6095,34 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6188,7 +6200,7 @@
       </c>
       <c r="E4" s="31" t="n">
         <f aca="false">COUNTIFS(Plan!$H$2:$H$600,A4,Plan!$K$2:$K$600,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="31" t="n">
         <f aca="false">SUMIF(Plan!$H$2:$H$600,A4,Plan!$G$2:$G$600)</f>
@@ -6610,7 +6622,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,B$4,Plan!$K$2:$K$600,"Done")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,C$4,Plan!$K$2:$K$600,"Done")</f>
@@ -6618,7 +6630,7 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">SUM(B8:C8)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6695,7 +6707,7 @@
       </c>
       <c r="B13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=B$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=C$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
@@ -6703,7 +6715,7 @@
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">SUM(B13:C13)</f>
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6712,7 +6724,7 @@
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">IFERROR(B13/B12,0)</f>
-        <v>0.586666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C13/C12,0)</f>
@@ -6720,7 +6732,7 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">IFERROR(D13/D12,0)</f>
-        <v>0.204651162790698</v>
+        <v>0.223255813953488</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6754,7 +6766,7 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Pass")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Pass")</f>
@@ -6762,7 +6774,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">SUM(B18:C18)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6805,7 +6817,7 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
@@ -6813,7 +6825,7 @@
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">SUM(B21:C21)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6822,7 +6834,7 @@
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IFERROR((B17-B21)/B17,0)</f>
-        <v>0.263157894736842</v>
+        <v>0.315789473684211</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">IFERROR((C17-C21)/C17,0)</f>
@@ -6830,7 +6842,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">IFERROR((D17-D21)/D17,0)</f>
-        <v>0.111111111111111</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8134,7 +8146,7 @@
       </c>
       <c r="D86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -8142,7 +8154,7 @@
       </c>
       <c r="F86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Not Run")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Not Run",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8321,7 +8333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{628D9AFD-2A27-48F9-82A7-3094233FDB95}</x14:id>
+          <x14:id>{2727D670-D348-4B3E-A1B4-53A79D40246B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8335,7 +8347,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1D7B3917-18F6-4CDC-8540-431268157140}</x14:id>
+          <x14:id>{69E32035-00FC-4C4A-A93A-2F791217EC87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8349,7 +8361,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6EE7B192-71F5-41DF-A982-A0FE7C137657}</x14:id>
+          <x14:id>{F9CF9955-43E3-45CD-AF72-BEEE5E28E7CD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8363,7 +8375,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{401810BF-4692-422B-B4B2-6D3EAAF5E42A}</x14:id>
+          <x14:id>{6CC2B4F0-103C-4653-9DD8-5C20F5FA29C3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8409,7 +8421,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{628D9AFD-2A27-48F9-82A7-3094233FDB95}">
+          <x14:cfRule type="dataBar" id="{2727D670-D348-4B3E-A1B4-53A79D40246B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8424,7 +8436,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1D7B3917-18F6-4CDC-8540-431268157140}">
+          <x14:cfRule type="dataBar" id="{69E32035-00FC-4C4A-A93A-2F791217EC87}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8439,7 +8451,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6EE7B192-71F5-41DF-A982-A0FE7C137657}">
+          <x14:cfRule type="dataBar" id="{F9CF9955-43E3-45CD-AF72-BEEE5E28E7CD}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8454,7 +8466,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{401810BF-4692-422B-B4B2-6D3EAAF5E42A}">
+          <x14:cfRule type="dataBar" id="{6CC2B4F0-103C-4653-9DD8-5C20F5FA29C3}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -9113,25 +9125,33 @@
         <v>46346</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="L11" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="L11" s="34" t="n">
+        <v>1</v>
+      </c>
       <c r="M11" s="35" t="n">
         <f aca="false">IF(K11="Done",1,IF(L11="",0,MIN(1,L11)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="33"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="36" t="n">
+        <v>46319</v>
+      </c>
       <c r="P11" s="31" t="str">
         <f aca="true">IF(K11="Done",IF(O11="","Done",IF(J11="","Done",IF(O11&lt;=J11,"On time","Late"))),IF(K11="Blocked","BLOCKED",IF(I11="","",IF(TODAY()&gt;J11,"OVERDUE",IF(TODAY()&gt;=I11,"Active","Upcoming")))))</f>
-        <v>Upcoming</v>
-      </c>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+        <v>On time</v>
+      </c>
+      <c r="Q11" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="R11" s="33" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -9140,10 +9160,10 @@
         <v>209</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F12" s="31" t="s">
         <v>168</v>
@@ -9163,7 +9183,7 @@
         <v>46353</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35" t="n">
@@ -9181,19 +9201,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>161</v>
@@ -9213,7 +9233,7 @@
         <v>46353</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="n">
@@ -9231,19 +9251,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F14" s="31" t="s">
         <v>161</v>
@@ -9263,7 +9283,7 @@
         <v>46353</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="n">
@@ -9281,19 +9301,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F15" s="31" t="s">
         <v>168</v>
@@ -9313,7 +9333,7 @@
         <v>46353</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="n">
@@ -9331,19 +9351,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F16" s="31" t="s">
         <v>161</v>
@@ -9363,7 +9383,7 @@
         <v>46353</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="n">
@@ -9381,22 +9401,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G17" s="31" t="n">
         <v>4</v>
@@ -9413,7 +9433,7 @@
         <v>46353</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35" t="n">
@@ -9431,7 +9451,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
@@ -9440,10 +9460,10 @@
         <v>165</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F18" s="31" t="s">
         <v>161</v>
@@ -9463,7 +9483,7 @@
         <v>46360</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="n">
@@ -9481,7 +9501,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -9490,10 +9510,10 @@
         <v>165</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F19" s="31" t="s">
         <v>161</v>
@@ -9513,7 +9533,7 @@
         <v>46360</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="n">
@@ -9531,7 +9551,7 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
@@ -9540,10 +9560,10 @@
         <v>165</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F20" s="31" t="s">
         <v>161</v>
@@ -9563,7 +9583,7 @@
         <v>46360</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="n">
@@ -9581,7 +9601,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
@@ -9590,10 +9610,10 @@
         <v>158</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F21" s="31" t="s">
         <v>161</v>
@@ -9613,7 +9633,7 @@
         <v>46367</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="n">
@@ -9631,7 +9651,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -9640,10 +9660,10 @@
         <v>158</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F22" s="31" t="s">
         <v>161</v>
@@ -9663,7 +9683,7 @@
         <v>46367</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="n">
@@ -9681,7 +9701,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -9690,10 +9710,10 @@
         <v>158</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>161</v>
@@ -9713,7 +9733,7 @@
         <v>46374</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="n">
@@ -9731,7 +9751,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -9740,10 +9760,10 @@
         <v>158</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F24" s="31" t="s">
         <v>161</v>
@@ -9763,7 +9783,7 @@
         <v>46381</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="n">
@@ -9781,7 +9801,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -9790,10 +9810,10 @@
         <v>158</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F25" s="31" t="s">
         <v>161</v>
@@ -9813,7 +9833,7 @@
         <v>46388</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="n">
@@ -9831,7 +9851,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -9840,10 +9860,10 @@
         <v>158</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F26" s="31" t="s">
         <v>161</v>
@@ -9863,7 +9883,7 @@
         <v>46388</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="n">
@@ -9881,7 +9901,7 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -9890,10 +9910,10 @@
         <v>158</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>161</v>
@@ -9913,7 +9933,7 @@
         <v>46395</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35" t="n">
@@ -9931,7 +9951,7 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -9940,10 +9960,10 @@
         <v>158</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F28" s="31" t="s">
         <v>168</v>
@@ -9963,7 +9983,7 @@
         <v>46395</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="35" t="n">
@@ -9981,7 +10001,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -9990,10 +10010,10 @@
         <v>158</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F29" s="31" t="s">
         <v>161</v>
@@ -10013,7 +10033,7 @@
         <v>46402</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="35" t="n">
@@ -10031,7 +10051,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -10040,10 +10060,10 @@
         <v>158</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F30" s="31" t="s">
         <v>168</v>
@@ -10063,7 +10083,7 @@
         <v>46402</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="35" t="n">
@@ -10081,19 +10101,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F31" s="31" t="s">
         <v>168</v>
@@ -10113,7 +10133,7 @@
         <v>46409</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="n">
@@ -10131,22 +10151,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G32" s="31" t="n">
         <v>8</v>
@@ -10163,7 +10183,7 @@
         <v>46409</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L32" s="34"/>
       <c r="M32" s="35" t="n">
@@ -10181,19 +10201,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F33" s="31" t="s">
         <v>161</v>
@@ -10213,7 +10233,7 @@
         <v>46409</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L33" s="34"/>
       <c r="M33" s="35" t="n">
@@ -10231,19 +10251,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F34" s="31" t="s">
         <v>161</v>
@@ -10263,7 +10283,7 @@
         <v>46416</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="35" t="n">
@@ -10281,19 +10301,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>161</v>
@@ -10313,7 +10333,7 @@
         <v>46416</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L35" s="34"/>
       <c r="M35" s="35" t="n">
@@ -10331,19 +10351,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F36" s="31" t="s">
         <v>161</v>
@@ -10363,7 +10383,7 @@
         <v>46423</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="n">
@@ -10381,7 +10401,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -10390,10 +10410,10 @@
         <v>209</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F37" s="31" t="s">
         <v>161</v>
@@ -10413,7 +10433,7 @@
         <v>46423</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="35" t="n">
@@ -10431,19 +10451,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F38" s="31" t="s">
         <v>161</v>
@@ -10463,7 +10483,7 @@
         <v>46423</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="n">
@@ -10481,19 +10501,19 @@
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F39" s="31" t="s">
         <v>168</v>
@@ -10513,7 +10533,7 @@
         <v>46423</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="35" t="n">
@@ -10531,19 +10551,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>168</v>
@@ -10563,7 +10583,7 @@
         <v>46423</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="35" t="n">
@@ -10621,7 +10641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2873B13A-6276-4CDE-AFC8-DCC4F9F58045}</x14:id>
+          <x14:id>{53D18D66-6D9A-4BF5-ABBF-52599145C127}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10652,7 +10672,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2873B13A-6276-4CDE-AFC8-DCC4F9F58045}">
+          <x14:cfRule type="dataBar" id="{53D18D66-6D9A-4BF5-ABBF-52599145C127}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10699,34 +10719,34 @@
         <v>88</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10737,31 +10757,31 @@
         <v>96</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10772,31 +10792,31 @@
         <v>96</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10807,31 +10827,31 @@
         <v>96</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="J4" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="K4" s="31" t="s">
         <v>334</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10842,31 +10862,31 @@
         <v>96</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10877,31 +10897,31 @@
         <v>96</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10912,31 +10932,31 @@
         <v>96</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10947,31 +10967,31 @@
         <v>96</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10982,31 +11002,31 @@
         <v>96</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11017,31 +11037,31 @@
         <v>96</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11052,31 +11072,31 @@
         <v>96</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11087,31 +11107,31 @@
         <v>96</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11122,31 +11142,31 @@
         <v>96</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11154,34 +11174,34 @@
         <v>103</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11189,34 +11209,34 @@
         <v>104</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11224,34 +11244,34 @@
         <v>105</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11262,31 +11282,31 @@
         <v>96</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11297,31 +11317,31 @@
         <v>209</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11332,31 +11352,31 @@
         <v>96</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11367,31 +11387,31 @@
         <v>96</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11402,31 +11422,31 @@
         <v>96</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11437,31 +11457,31 @@
         <v>96</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11472,31 +11492,31 @@
         <v>96</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11504,34 +11524,34 @@
         <v>113</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11539,34 +11559,34 @@
         <v>114</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J25" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11574,34 +11594,34 @@
         <v>115</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J26" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11609,34 +11629,34 @@
         <v>116</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J27" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11644,34 +11664,34 @@
         <v>117</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J28" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11679,34 +11699,34 @@
         <v>118</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11714,34 +11734,34 @@
         <v>119</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11749,34 +11769,34 @@
         <v>120</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J31" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11784,34 +11804,34 @@
         <v>121</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I32" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J32" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11819,34 +11839,34 @@
         <v>122</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J33" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11854,34 +11874,34 @@
         <v>123</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K34" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11889,34 +11909,34 @@
         <v>124</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K35" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11924,34 +11944,34 @@
         <v>125</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I36" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J36" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K36" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11959,34 +11979,34 @@
         <v>126</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I37" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11997,31 +12017,31 @@
         <v>209</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I38" s="31" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K38" s="31" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12032,31 +12052,31 @@
         <v>209</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K39" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12067,31 +12087,31 @@
         <v>209</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12102,31 +12122,31 @@
         <v>209</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K41" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12137,31 +12157,31 @@
         <v>209</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12172,31 +12192,31 @@
         <v>209</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J43" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K43" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12207,31 +12227,31 @@
         <v>209</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12239,34 +12259,34 @@
         <v>134</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J45" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="K45" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12274,34 +12294,34 @@
         <v>135</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K46" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12309,34 +12329,34 @@
         <v>136</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12347,31 +12367,31 @@
         <v>96</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I48" s="31" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -12426,7 +12446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -12438,42 +12458,42 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -12486,40 +12506,40 @@
         <v>Grey</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>161</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46336</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="28" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -12535,37 +12555,37 @@
         <v>197</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I3" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L3" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N3" s="33"/>
       <c r="O3" s="33" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -12581,19 +12601,19 @@
         <v>203</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I4" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K4" s="33" t="s">
         <v>59</v>
@@ -12602,7 +12622,7 @@
         <v>46319</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N4" s="33"/>
       <c r="O4" s="33" t="s">
@@ -12611,7 +12631,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
@@ -12624,34 +12644,40 @@
         <v>Black</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I5" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="36"/>
-      <c r="M5" s="33"/>
+        <v>376</v>
+      </c>
+      <c r="L5" s="36" t="n">
+        <v>46319</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>614</v>
+      </c>
       <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
+      <c r="O5" s="33" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
@@ -12664,22 +12690,22 @@
         <v>Black</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I6" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K6" s="33" t="s">
         <v>68</v>
@@ -12691,7 +12717,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
@@ -12704,22 +12730,22 @@
         <v>White</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I7" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K7" s="33" t="s">
         <v>68</v>
@@ -12731,7 +12757,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
@@ -12744,31 +12770,31 @@
         <v>White</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L8" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="N8" s="33"/>
       <c r="O8" s="33" t="s">
@@ -12777,7 +12803,7 @@
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -12790,40 +12816,40 @@
         <v>White</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L9" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
@@ -12836,22 +12862,22 @@
         <v>Black</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>68</v>
@@ -12863,7 +12889,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
@@ -12876,22 +12902,22 @@
         <v>Black</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>68</v>
@@ -12903,7 +12929,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -12916,22 +12942,22 @@
         <v>Grey</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>68</v>
@@ -12943,7 +12969,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
@@ -12956,22 +12982,22 @@
         <v>Grey</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I13" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>68</v>
@@ -12983,7 +13009,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
@@ -12996,22 +13022,22 @@
         <v>Grey</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="I14" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>68</v>
@@ -13023,7 +13049,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
@@ -13036,22 +13062,22 @@
         <v>White</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>68</v>
@@ -13063,7 +13089,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
@@ -13076,31 +13102,31 @@
         <v>White</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L16" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="N16" s="33"/>
       <c r="O16" s="33" t="s">
@@ -13109,7 +13135,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
@@ -13122,22 +13148,22 @@
         <v>Black</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="I17" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>68</v>
@@ -13149,7 +13175,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>5</v>
@@ -13162,22 +13188,22 @@
         <v>Grey</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I18" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>68</v>
@@ -13189,7 +13215,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>5</v>
@@ -13202,22 +13228,22 @@
         <v>Grey</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="I19" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>68</v>
@@ -13229,7 +13255,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>5</v>
@@ -13245,19 +13271,19 @@
         <v>5</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>68</v>
@@ -13269,7 +13295,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>5</v>
@@ -13282,22 +13308,22 @@
         <v>Black</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K21" s="33" t="s">
         <v>68</v>
@@ -13309,7 +13335,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -13322,22 +13348,22 @@
         <v>White</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>68</v>
@@ -13349,7 +13375,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -13362,22 +13388,22 @@
         <v>White</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I23" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>68</v>
@@ -13389,7 +13415,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -13402,22 +13428,22 @@
         <v>White</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="I24" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>68</v>
@@ -13429,7 +13455,7 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -13442,22 +13468,22 @@
         <v>Black</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I25" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K25" s="33" t="s">
         <v>68</v>
@@ -13469,7 +13495,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -13482,22 +13508,22 @@
         <v>Grey</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I26" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>68</v>
@@ -13509,7 +13535,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -13522,22 +13548,22 @@
         <v>White</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I27" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K27" s="33" t="s">
         <v>68</v>
@@ -13549,7 +13575,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -13562,22 +13588,22 @@
         <v>Black</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I28" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K28" s="33" t="s">
         <v>68</v>
@@ -13589,7 +13615,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -13602,22 +13628,22 @@
         <v>Grey</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K29" s="33" t="s">
         <v>68</v>
@@ -13629,7 +13655,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -13642,22 +13668,22 @@
         <v>Black</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I30" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K30" s="33" t="s">
         <v>68</v>
@@ -13669,7 +13695,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
@@ -13682,22 +13708,22 @@
         <v>Black</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I31" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K31" s="33" t="s">
         <v>68</v>
@@ -13709,7 +13735,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
@@ -13722,22 +13748,22 @@
         <v>White</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I32" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K32" s="33" t="s">
         <v>68</v>
@@ -13749,7 +13775,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
@@ -13762,22 +13788,22 @@
         <v>Black</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I33" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K33" s="33" t="s">
         <v>68</v>
@@ -13789,7 +13815,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
@@ -13802,22 +13828,22 @@
         <v>Grey</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="I34" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K34" s="33" t="s">
         <v>68</v>
@@ -13829,7 +13855,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
@@ -13842,22 +13868,22 @@
         <v>Black</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I35" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K35" s="33" t="s">
         <v>68</v>
@@ -13869,7 +13895,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
@@ -13882,22 +13908,22 @@
         <v>Grey</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I36" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K36" s="33" t="s">
         <v>68</v>
@@ -13909,7 +13935,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -13922,22 +13948,22 @@
         <v>Black</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I37" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K37" s="33" t="s">
         <v>68</v>
@@ -13949,7 +13975,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
@@ -13962,22 +13988,22 @@
         <v>Grey</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I38" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K38" s="33" t="s">
         <v>68</v>
@@ -13989,7 +14015,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
@@ -14002,22 +14028,22 @@
         <v>Black</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I39" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K39" s="33" t="s">
         <v>68</v>
@@ -14029,7 +14055,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
@@ -14042,22 +14068,22 @@
         <v>Black</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K40" s="33" t="s">
         <v>68</v>
@@ -14069,7 +14095,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>7</v>
@@ -14082,22 +14108,22 @@
         <v>Black</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="I41" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K41" s="33" t="s">
         <v>68</v>
@@ -14109,7 +14135,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>7</v>
@@ -14122,22 +14148,22 @@
         <v>Black</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I42" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K42" s="33" t="s">
         <v>68</v>
@@ -14149,7 +14175,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>7</v>
@@ -14162,22 +14188,22 @@
         <v>Black</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I43" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K43" s="33" t="s">
         <v>68</v>
@@ -14189,7 +14215,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>7</v>
@@ -14202,22 +14228,22 @@
         <v>Black</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I44" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K44" s="33" t="s">
         <v>68</v>
@@ -14229,7 +14255,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
@@ -14242,22 +14268,22 @@
         <v>Black</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I45" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K45" s="33" t="s">
         <v>68</v>
@@ -14269,7 +14295,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>7</v>
@@ -14282,22 +14308,22 @@
         <v>Black</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I46" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K46" s="33" t="s">
         <v>68</v>
@@ -14309,7 +14335,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>7</v>
@@ -14322,22 +14348,22 @@
         <v>Black</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="I47" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K47" s="33" t="s">
         <v>68</v>
@@ -14414,43 +14440,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>155</v>
@@ -14458,7 +14484,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -14467,16 +14493,16 @@
         <v>42</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F2" s="37" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H2" s="37" t="n">
         <v>38</v>
@@ -14486,40 +14512,40 @@
         <v>PASS</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46338</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="N2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F3" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H3" s="39"/>
       <c r="I3" s="31" t="str">
@@ -14527,7 +14553,7 @@
         <v>PENDING</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
@@ -14536,7 +14562,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -14545,16 +14571,16 @@
         <v>42</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F4" s="40" t="n">
         <v>300</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="31" t="str">
@@ -14562,7 +14588,7 @@
         <v>PENDING</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="36"/>
@@ -14571,25 +14597,25 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F5" s="40" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H5" s="41" t="n">
         <v>3.3</v>
@@ -14599,42 +14625,42 @@
         <v>PASS</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F6" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="31" t="str">
@@ -14642,7 +14668,7 @@
         <v>PENDING</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="36"/>
@@ -14651,25 +14677,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H7" s="39"/>
       <c r="I7" s="31" t="str">
@@ -14677,7 +14703,7 @@
         <v>PENDING</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
@@ -14686,25 +14712,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="31" t="str">
@@ -14712,7 +14738,7 @@
         <v>PENDING</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="36"/>
@@ -14721,7 +14747,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -14730,16 +14756,16 @@
         <v>209</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="H9" s="41"/>
       <c r="I9" s="31" t="str">
@@ -14747,7 +14773,7 @@
         <v>PENDING</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
@@ -14756,25 +14782,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="31" t="str">
@@ -14782,7 +14808,7 @@
         <v>PENDING</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="36"/>
@@ -14791,25 +14817,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="31" t="str">
@@ -14817,7 +14843,7 @@
         <v>PENDING</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="36"/>
@@ -14826,25 +14852,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F12" s="40" t="n">
         <v>10000</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="31" t="str">
@@ -14852,7 +14878,7 @@
         <v>PENDING</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K12" s="33"/>
       <c r="L12" s="36"/>
@@ -14861,7 +14887,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>7</v>
@@ -14870,16 +14896,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F13" s="40" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="31" t="str">
@@ -14887,7 +14913,7 @@
         <v>PENDING</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="36"/>
@@ -14896,7 +14922,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>7</v>
@@ -14905,16 +14931,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="31" t="str">
@@ -14922,7 +14948,7 @@
         <v>PENDING</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="36"/>
@@ -14931,25 +14957,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>0.001</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="31" t="str">
@@ -14957,7 +14983,7 @@
         <v>PENDING</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K15" s="33"/>
       <c r="L15" s="36"/>
@@ -14966,25 +14992,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="31" t="str">
@@ -14992,7 +15018,7 @@
         <v>PENDING</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="36"/>
@@ -15001,25 +15027,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="31" t="str">
@@ -15027,7 +15053,7 @@
         <v>PENDING</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="36"/>
@@ -15036,25 +15062,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="31" t="str">
@@ -15062,7 +15088,7 @@
         <v>PENDING</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="36"/>
@@ -15071,7 +15097,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -15080,16 +15106,16 @@
         <v>42</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="31" t="str">
@@ -15097,7 +15123,7 @@
         <v>PENDING</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="36"/>
@@ -15106,25 +15132,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>15</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="31" t="str">
@@ -15132,7 +15158,7 @@
         <v>PENDING</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
@@ -15141,25 +15167,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="31" t="str">
@@ -15167,7 +15193,7 @@
         <v>PENDING</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="36"/>
@@ -15176,25 +15202,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0.75</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="31" t="str">
@@ -15202,7 +15228,7 @@
         <v>PENDING</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="36"/>
@@ -15211,25 +15237,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>0.9995</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="H23" s="39"/>
       <c r="I23" s="31" t="str">
@@ -15237,7 +15263,7 @@
         <v>PENDING</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="36"/>
@@ -15308,7 +15334,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -15317,69 +15343,69 @@
         <v>88</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -15388,13 +15414,13 @@
         <v>114</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G2" s="28" t="n">
         <v>30</v>
@@ -15444,15 +15470,15 @@
         <v>46338</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -15461,13 +15487,13 @@
         <v>114</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>15</v>
@@ -15503,7 +15529,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -15512,13 +15538,13 @@
         <v>116</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G4" s="31" t="n">
         <v>5</v>
@@ -15554,7 +15580,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
@@ -15563,13 +15589,13 @@
         <v>114</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>30</v>
@@ -15605,7 +15631,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
@@ -15614,13 +15640,13 @@
         <v>115</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>30</v>
@@ -15656,7 +15682,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
@@ -15665,13 +15691,13 @@
         <v>116</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>5</v>
@@ -15707,7 +15733,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
@@ -15716,13 +15742,13 @@
         <v>117</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>480</v>
@@ -15758,7 +15784,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -15767,13 +15793,13 @@
         <v>118</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G9" s="31" t="n">
         <v>30</v>
@@ -15809,7 +15835,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>7</v>
@@ -15818,13 +15844,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G10" s="31" t="n">
         <v>15</v>
@@ -15911,72 +15937,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="I2" s="28" t="n">
         <v>12</v>
@@ -15985,7 +16011,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46340</v>
@@ -15995,30 +16021,30 @@
         <v>PASS</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
@@ -16035,25 +16061,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
@@ -16070,25 +16096,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
@@ -16105,25 +16131,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
@@ -16140,25 +16166,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -16175,25 +16201,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
@@ -16210,25 +16236,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -16301,40 +16327,40 @@
         <v>140</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16342,13 +16368,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E2" s="30" t="n">
         <v>0.93</v>
@@ -16376,7 +16402,7 @@
         <v>46346</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16384,13 +16410,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
@@ -16416,13 +16442,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>975</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>971</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>967</v>
-      </c>
       <c r="D4" s="31" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -16448,13 +16474,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -16480,13 +16506,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
+        <v>976</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>972</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>967</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>968</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -16512,13 +16538,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16544,13 +16570,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1004">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -816,19 +816,25 @@
     <t xml:space="preserve">Plaintext pod-to-pod traffic rejected</t>
   </si>
   <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40091917398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoD: plaintext pod-to-pod traffic is rejected. A pod outside the mesh, in the same namespace (admitted by the NetworkPolicy), is refused by strict mTLS; ztunnel logs 'explicitly denied by: istio-system/istio_converted_static_strict', asserted in the GitOps e2e on kind (CI run 40089193779, 34/34) and on EKS (run 40091917398: 107/107, 107 resources applied and destroyed). Control experiment: PERMISSIVE let the same plaintext pod through, STRICT refused it. In-mesh traffic carries SPIFFE identities, incl. identity -&gt; Keycloak as spiffe://cluster.local/ns/meterbook-dev/sa/identity. Built: ADR-0011 (Linkerd vs Istio sidecars vs Istio ambient); Istio 1.31.3 ambient via ArgoCD (charts from ghcr.io OCI, images from mirror.gcr.io); platform-mesh chart (STRICT, namespace enrolment from Git, never pruned); NetworkPolicies admit HBONE 15008 and mesh probe address only; render tests. Found and fixed: Istio 1.31 left gcr.io; ambient needs 15008 and 169.254.7.127 in NetworkPolicies; in-cluster verification lost output (kubectl run -i race), now run to completion and read from logs. Prod gets the mesh with its environment. Evidence: docs/evidence/2026-10-24-service-mesh-mtls.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB-T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBAC + customer-facing audit log service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every mutating endpoint emits an audit event</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not Started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB-T11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBAC + customer-facing audit log service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every mutating endpoint emits an audit event</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T12</t>
@@ -4269,60 +4275,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4335,13 +4341,13 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6095,34 +6101,34 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6229,7 +6235,7 @@
       </c>
       <c r="E5" s="31" t="n">
         <f aca="false">COUNTIFS(Plan!$H$2:$H$600,A5,Plan!$K$2:$K$600,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="31" t="n">
         <f aca="false">SUMIF(Plan!$H$2:$H$600,A5,Plan!$G$2:$G$600)</f>
@@ -6622,7 +6628,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,B$4,Plan!$K$2:$K$600,"Done")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIFS(Plan!$B$2:$B$600,C$4,Plan!$K$2:$K$600,"Done")</f>
@@ -6630,7 +6636,7 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">SUM(B8:C8)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6707,7 +6713,7 @@
       </c>
       <c r="B13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=B$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">SUMPRODUCT((Plan!$B$2:$B$600=C$4)*Plan!$G$2:$G$600*Plan!$M$2:$M$600)</f>
@@ -6715,7 +6721,7 @@
       </c>
       <c r="D13" s="21" t="n">
         <f aca="false">SUM(B13:C13)</f>
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6724,7 +6730,7 @@
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">IFERROR(B13/B12,0)</f>
-        <v>0.64</v>
+        <v>0.693333333333333</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C13/C12,0)</f>
@@ -6732,7 +6738,7 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">IFERROR(D13/D12,0)</f>
-        <v>0.223255813953488</v>
+        <v>0.241860465116279</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8333,7 +8339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2727D670-D348-4B3E-A1B4-53A79D40246B}</x14:id>
+          <x14:id>{71B98949-D6D7-44F3-8360-3118E843C836}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8347,7 +8353,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69E32035-00FC-4C4A-A93A-2F791217EC87}</x14:id>
+          <x14:id>{8219F0EC-4BDA-43B7-A77C-E3E6C200ADEE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8361,7 +8367,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F9CF9955-43E3-45CD-AF72-BEEE5E28E7CD}</x14:id>
+          <x14:id>{D6F31996-A280-40E7-B386-25F134B1DBE6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8375,7 +8381,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6CC2B4F0-103C-4653-9DD8-5C20F5FA29C3}</x14:id>
+          <x14:id>{607D3F38-9D15-4585-835C-6AD750874E71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8421,7 +8427,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2727D670-D348-4B3E-A1B4-53A79D40246B}">
+          <x14:cfRule type="dataBar" id="{71B98949-D6D7-44F3-8360-3118E843C836}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8436,7 +8442,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{69E32035-00FC-4C4A-A93A-2F791217EC87}">
+          <x14:cfRule type="dataBar" id="{8219F0EC-4BDA-43B7-A77C-E3E6C200ADEE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8451,7 +8457,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F9CF9955-43E3-45CD-AF72-BEEE5E28E7CD}">
+          <x14:cfRule type="dataBar" id="{D6F31996-A280-40E7-B386-25F134B1DBE6}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8466,7 +8472,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6CC2B4F0-103C-4653-9DD8-5C20F5FA29C3}">
+          <x14:cfRule type="dataBar" id="{607D3F38-9D15-4585-835C-6AD750874E71}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -9183,37 +9189,45 @@
         <v>46353</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="L12" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="L12" s="34" t="n">
+        <v>1</v>
+      </c>
       <c r="M12" s="35" t="n">
         <f aca="false">IF(K12="Done",1,IF(L12="",0,MIN(1,L12)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="33"/>
-      <c r="O12" s="36"/>
+      <c r="O12" s="36" t="n">
+        <v>46319</v>
+      </c>
       <c r="P12" s="31" t="str">
         <f aca="true">IF(K12="Done",IF(O12="","Done",IF(J12="","Done",IF(O12&lt;=J12,"On time","Late"))),IF(K12="Blocked","BLOCKED",IF(I12="","",IF(TODAY()&gt;J12,"OVERDUE",IF(TODAY()&gt;=I12,"Active","Upcoming")))))</f>
-        <v>Upcoming</v>
-      </c>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+        <v>On time</v>
+      </c>
+      <c r="Q12" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="R12" s="33" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>161</v>
@@ -9233,7 +9247,7 @@
         <v>46353</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="n">
@@ -9251,19 +9265,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F14" s="31" t="s">
         <v>161</v>
@@ -9283,7 +9297,7 @@
         <v>46353</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="n">
@@ -9301,19 +9315,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F15" s="31" t="s">
         <v>168</v>
@@ -9333,7 +9347,7 @@
         <v>46353</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="n">
@@ -9351,19 +9365,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F16" s="31" t="s">
         <v>161</v>
@@ -9383,7 +9397,7 @@
         <v>46353</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="n">
@@ -9401,22 +9415,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G17" s="31" t="n">
         <v>4</v>
@@ -9433,7 +9447,7 @@
         <v>46353</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35" t="n">
@@ -9451,7 +9465,7 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
@@ -9460,10 +9474,10 @@
         <v>165</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F18" s="31" t="s">
         <v>161</v>
@@ -9483,7 +9497,7 @@
         <v>46360</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="n">
@@ -9501,7 +9515,7 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -9510,10 +9524,10 @@
         <v>165</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F19" s="31" t="s">
         <v>161</v>
@@ -9533,7 +9547,7 @@
         <v>46360</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="n">
@@ -9551,7 +9565,7 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
@@ -9560,10 +9574,10 @@
         <v>165</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F20" s="31" t="s">
         <v>161</v>
@@ -9583,7 +9597,7 @@
         <v>46360</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="n">
@@ -9601,7 +9615,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
@@ -9610,10 +9624,10 @@
         <v>158</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F21" s="31" t="s">
         <v>161</v>
@@ -9633,7 +9647,7 @@
         <v>46367</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="n">
@@ -9651,7 +9665,7 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -9660,10 +9674,10 @@
         <v>158</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F22" s="31" t="s">
         <v>161</v>
@@ -9683,7 +9697,7 @@
         <v>46367</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="n">
@@ -9701,7 +9715,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -9710,10 +9724,10 @@
         <v>158</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>161</v>
@@ -9733,7 +9747,7 @@
         <v>46374</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="n">
@@ -9751,7 +9765,7 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -9760,10 +9774,10 @@
         <v>158</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F24" s="31" t="s">
         <v>161</v>
@@ -9783,7 +9797,7 @@
         <v>46381</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="n">
@@ -9801,7 +9815,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -9810,10 +9824,10 @@
         <v>158</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F25" s="31" t="s">
         <v>161</v>
@@ -9833,7 +9847,7 @@
         <v>46388</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="n">
@@ -9851,7 +9865,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -9860,10 +9874,10 @@
         <v>158</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F26" s="31" t="s">
         <v>161</v>
@@ -9883,7 +9897,7 @@
         <v>46388</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="n">
@@ -9901,7 +9915,7 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -9910,10 +9924,10 @@
         <v>158</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>161</v>
@@ -9933,7 +9947,7 @@
         <v>46395</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35" t="n">
@@ -9951,7 +9965,7 @@
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -9960,10 +9974,10 @@
         <v>158</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F28" s="31" t="s">
         <v>168</v>
@@ -9983,7 +9997,7 @@
         <v>46395</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="35" t="n">
@@ -10001,7 +10015,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -10010,10 +10024,10 @@
         <v>158</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F29" s="31" t="s">
         <v>161</v>
@@ -10033,7 +10047,7 @@
         <v>46402</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L29" s="34"/>
       <c r="M29" s="35" t="n">
@@ -10051,7 +10065,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -10060,10 +10074,10 @@
         <v>158</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F30" s="31" t="s">
         <v>168</v>
@@ -10083,7 +10097,7 @@
         <v>46402</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L30" s="34"/>
       <c r="M30" s="35" t="n">
@@ -10101,19 +10115,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F31" s="31" t="s">
         <v>168</v>
@@ -10133,7 +10147,7 @@
         <v>46409</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="n">
@@ -10151,22 +10165,22 @@
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G32" s="31" t="n">
         <v>8</v>
@@ -10183,7 +10197,7 @@
         <v>46409</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L32" s="34"/>
       <c r="M32" s="35" t="n">
@@ -10201,19 +10215,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F33" s="31" t="s">
         <v>161</v>
@@ -10233,7 +10247,7 @@
         <v>46409</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L33" s="34"/>
       <c r="M33" s="35" t="n">
@@ -10251,19 +10265,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F34" s="31" t="s">
         <v>161</v>
@@ -10283,7 +10297,7 @@
         <v>46416</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="35" t="n">
@@ -10301,19 +10315,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>161</v>
@@ -10333,7 +10347,7 @@
         <v>46416</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L35" s="34"/>
       <c r="M35" s="35" t="n">
@@ -10351,19 +10365,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F36" s="31" t="s">
         <v>161</v>
@@ -10383,7 +10397,7 @@
         <v>46423</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="n">
@@ -10401,7 +10415,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -10410,10 +10424,10 @@
         <v>209</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F37" s="31" t="s">
         <v>161</v>
@@ -10433,7 +10447,7 @@
         <v>46423</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="35" t="n">
@@ -10451,19 +10465,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F38" s="31" t="s">
         <v>161</v>
@@ -10483,7 +10497,7 @@
         <v>46423</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="n">
@@ -10501,19 +10515,19 @@
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F39" s="31" t="s">
         <v>168</v>
@@ -10533,7 +10547,7 @@
         <v>46423</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="35" t="n">
@@ -10551,19 +10565,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F40" s="31" t="s">
         <v>168</v>
@@ -10583,7 +10597,7 @@
         <v>46423</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="L40" s="34"/>
       <c r="M40" s="35" t="n">
@@ -10641,7 +10655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53D18D66-6D9A-4BF5-ABBF-52599145C127}</x14:id>
+          <x14:id>{F69AD8A5-E010-4990-B3A8-E2E633EE8FBA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10672,7 +10686,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53D18D66-6D9A-4BF5-ABBF-52599145C127}">
+          <x14:cfRule type="dataBar" id="{F69AD8A5-E010-4990-B3A8-E2E633EE8FBA}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10719,34 +10733,34 @@
         <v>88</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>89</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10757,31 +10771,31 @@
         <v>96</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10792,31 +10806,31 @@
         <v>96</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10827,31 +10841,31 @@
         <v>96</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="J4" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="E4" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="K4" s="31" t="s">
         <v>336</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10862,31 +10876,31 @@
         <v>96</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10897,31 +10911,31 @@
         <v>96</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10932,31 +10946,31 @@
         <v>96</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10967,31 +10981,31 @@
         <v>96</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11002,31 +11016,31 @@
         <v>96</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11037,31 +11051,31 @@
         <v>96</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11072,31 +11086,31 @@
         <v>96</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11107,31 +11121,31 @@
         <v>96</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11142,31 +11156,31 @@
         <v>96</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11174,34 +11188,34 @@
         <v>103</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11209,34 +11223,34 @@
         <v>104</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11244,34 +11258,34 @@
         <v>105</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11282,31 +11296,31 @@
         <v>96</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I17" s="31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11317,31 +11331,31 @@
         <v>209</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11352,31 +11366,31 @@
         <v>96</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11387,31 +11401,31 @@
         <v>96</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11422,31 +11436,31 @@
         <v>96</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11457,31 +11471,31 @@
         <v>96</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11492,31 +11506,31 @@
         <v>96</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11524,34 +11538,34 @@
         <v>113</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11559,34 +11573,34 @@
         <v>114</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J25" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11594,34 +11608,34 @@
         <v>115</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J26" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11629,34 +11643,34 @@
         <v>116</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J27" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11664,34 +11678,34 @@
         <v>117</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J28" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11699,34 +11713,34 @@
         <v>118</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11734,34 +11748,34 @@
         <v>119</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J30" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11769,34 +11783,34 @@
         <v>120</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J31" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11804,34 +11818,34 @@
         <v>121</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I32" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J32" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11839,34 +11853,34 @@
         <v>122</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J33" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11874,34 +11888,34 @@
         <v>123</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K34" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11909,34 +11923,34 @@
         <v>124</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I35" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J35" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K35" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11944,34 +11958,34 @@
         <v>125</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I36" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J36" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K36" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11979,34 +11993,34 @@
         <v>126</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I37" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K37" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12017,31 +12031,31 @@
         <v>209</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I38" s="31" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K38" s="31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12052,31 +12066,31 @@
         <v>209</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K39" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12087,31 +12101,31 @@
         <v>209</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J40" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12122,31 +12136,31 @@
         <v>209</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I41" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K41" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12157,31 +12171,31 @@
         <v>209</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12192,31 +12206,31 @@
         <v>209</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J43" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K43" s="31" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12227,31 +12241,31 @@
         <v>209</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J44" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12259,34 +12273,34 @@
         <v>134</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J45" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K45" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12294,34 +12308,34 @@
         <v>135</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K46" s="31" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12329,34 +12343,34 @@
         <v>136</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12367,31 +12381,31 @@
         <v>96</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I48" s="31" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J48" s="31" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -12446,7 +12460,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -12458,42 +12472,42 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -12506,40 +12520,40 @@
         <v>Grey</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>161</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46336</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="28" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -12555,37 +12569,37 @@
         <v>197</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I3" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L3" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N3" s="33"/>
       <c r="O3" s="33" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -12601,19 +12615,19 @@
         <v>203</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I4" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K4" s="33" t="s">
         <v>59</v>
@@ -12622,7 +12636,7 @@
         <v>46319</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N4" s="33"/>
       <c r="O4" s="33" t="s">
@@ -12631,7 +12645,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
@@ -12644,40 +12658,40 @@
         <v>Black</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I5" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N5" s="33"/>
       <c r="O5" s="33" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
@@ -12690,22 +12704,22 @@
         <v>Black</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I6" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K6" s="33" t="s">
         <v>68</v>
@@ -12717,7 +12731,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
@@ -12730,22 +12744,22 @@
         <v>White</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I7" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K7" s="33" t="s">
         <v>68</v>
@@ -12757,7 +12771,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
@@ -12770,31 +12784,31 @@
         <v>White</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L8" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N8" s="33"/>
       <c r="O8" s="33" t="s">
@@ -12803,7 +12817,7 @@
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -12816,40 +12830,40 @@
         <v>White</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L9" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
@@ -12862,22 +12876,22 @@
         <v>Black</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>68</v>
@@ -12889,7 +12903,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
@@ -12902,22 +12916,22 @@
         <v>Black</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>68</v>
@@ -12929,7 +12943,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -12942,22 +12956,22 @@
         <v>Grey</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>68</v>
@@ -12969,7 +12983,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
@@ -12982,22 +12996,22 @@
         <v>Grey</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I13" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>68</v>
@@ -13009,7 +13023,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
@@ -13022,22 +13036,22 @@
         <v>Grey</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I14" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>68</v>
@@ -13049,7 +13063,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
@@ -13062,22 +13076,22 @@
         <v>White</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>68</v>
@@ -13089,7 +13103,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
@@ -13102,31 +13116,31 @@
         <v>White</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L16" s="36" t="n">
         <v>46319</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="N16" s="33"/>
       <c r="O16" s="33" t="s">
@@ -13135,7 +13149,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
@@ -13148,22 +13162,22 @@
         <v>Black</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I17" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>68</v>
@@ -13175,7 +13189,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>5</v>
@@ -13188,22 +13202,22 @@
         <v>Grey</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I18" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>68</v>
@@ -13215,7 +13229,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>5</v>
@@ -13228,22 +13242,22 @@
         <v>Grey</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I19" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>68</v>
@@ -13255,7 +13269,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>5</v>
@@ -13271,19 +13285,19 @@
         <v>5</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>68</v>
@@ -13295,7 +13309,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>5</v>
@@ -13308,22 +13322,22 @@
         <v>Black</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K21" s="33" t="s">
         <v>68</v>
@@ -13335,7 +13349,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -13348,22 +13362,22 @@
         <v>White</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>68</v>
@@ -13375,7 +13389,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -13388,22 +13402,22 @@
         <v>White</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I23" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>68</v>
@@ -13415,7 +13429,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -13428,22 +13442,22 @@
         <v>White</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I24" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>68</v>
@@ -13455,7 +13469,7 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -13468,22 +13482,22 @@
         <v>Black</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I25" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K25" s="33" t="s">
         <v>68</v>
@@ -13495,7 +13509,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -13508,22 +13522,22 @@
         <v>Grey</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I26" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>68</v>
@@ -13535,7 +13549,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -13548,22 +13562,22 @@
         <v>White</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I27" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K27" s="33" t="s">
         <v>68</v>
@@ -13575,7 +13589,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -13588,22 +13602,22 @@
         <v>Black</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I28" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K28" s="33" t="s">
         <v>68</v>
@@ -13615,7 +13629,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -13628,22 +13642,22 @@
         <v>Grey</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K29" s="33" t="s">
         <v>68</v>
@@ -13655,7 +13669,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -13668,22 +13682,22 @@
         <v>Black</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I30" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K30" s="33" t="s">
         <v>68</v>
@@ -13695,7 +13709,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
@@ -13708,22 +13722,22 @@
         <v>Black</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I31" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K31" s="33" t="s">
         <v>68</v>
@@ -13735,7 +13749,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
@@ -13748,22 +13762,22 @@
         <v>White</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I32" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K32" s="33" t="s">
         <v>68</v>
@@ -13775,7 +13789,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
@@ -13788,22 +13802,22 @@
         <v>Black</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I33" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K33" s="33" t="s">
         <v>68</v>
@@ -13815,7 +13829,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
@@ -13828,22 +13842,22 @@
         <v>Grey</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I34" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K34" s="33" t="s">
         <v>68</v>
@@ -13855,7 +13869,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
@@ -13868,22 +13882,22 @@
         <v>Black</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I35" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K35" s="33" t="s">
         <v>68</v>
@@ -13895,7 +13909,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
@@ -13908,22 +13922,22 @@
         <v>Grey</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I36" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K36" s="33" t="s">
         <v>68</v>
@@ -13935,7 +13949,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -13948,22 +13962,22 @@
         <v>Black</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I37" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K37" s="33" t="s">
         <v>68</v>
@@ -13975,7 +13989,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
@@ -13988,22 +14002,22 @@
         <v>Grey</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I38" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K38" s="33" t="s">
         <v>68</v>
@@ -14015,7 +14029,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
@@ -14028,22 +14042,22 @@
         <v>Black</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I39" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K39" s="33" t="s">
         <v>68</v>
@@ -14055,7 +14069,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
@@ -14068,22 +14082,22 @@
         <v>Black</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K40" s="33" t="s">
         <v>68</v>
@@ -14095,7 +14109,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>7</v>
@@ -14108,22 +14122,22 @@
         <v>Black</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I41" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K41" s="33" t="s">
         <v>68</v>
@@ -14135,7 +14149,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>7</v>
@@ -14148,22 +14162,22 @@
         <v>Black</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I42" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K42" s="33" t="s">
         <v>68</v>
@@ -14175,7 +14189,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>7</v>
@@ -14188,22 +14202,22 @@
         <v>Black</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I43" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K43" s="33" t="s">
         <v>68</v>
@@ -14215,7 +14229,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>7</v>
@@ -14228,22 +14242,22 @@
         <v>Black</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I44" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K44" s="33" t="s">
         <v>68</v>
@@ -14255,7 +14269,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
@@ -14268,22 +14282,22 @@
         <v>Black</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I45" s="31" t="s">
         <v>161</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K45" s="33" t="s">
         <v>68</v>
@@ -14295,7 +14309,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>7</v>
@@ -14308,22 +14322,22 @@
         <v>Black</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I46" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K46" s="33" t="s">
         <v>68</v>
@@ -14335,7 +14349,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>7</v>
@@ -14348,22 +14362,22 @@
         <v>Black</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="I47" s="31" t="s">
         <v>168</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K47" s="33" t="s">
         <v>68</v>
@@ -14440,43 +14454,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>155</v>
@@ -14484,7 +14498,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -14493,16 +14507,16 @@
         <v>42</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F2" s="37" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H2" s="37" t="n">
         <v>38</v>
@@ -14512,40 +14526,40 @@
         <v>PASS</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46338</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F3" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H3" s="39"/>
       <c r="I3" s="31" t="str">
@@ -14553,7 +14567,7 @@
         <v>PENDING</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
@@ -14562,7 +14576,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -14571,16 +14585,16 @@
         <v>42</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F4" s="40" t="n">
         <v>300</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="31" t="str">
@@ -14588,7 +14602,7 @@
         <v>PENDING</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K4" s="33"/>
       <c r="L4" s="36"/>
@@ -14597,25 +14611,25 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F5" s="40" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H5" s="41" t="n">
         <v>3.3</v>
@@ -14625,42 +14639,42 @@
         <v>PASS</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F6" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="31" t="str">
@@ -14668,7 +14682,7 @@
         <v>PENDING</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="36"/>
@@ -14677,25 +14691,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H7" s="39"/>
       <c r="I7" s="31" t="str">
@@ -14703,7 +14717,7 @@
         <v>PENDING</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
@@ -14712,25 +14726,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="31" t="str">
@@ -14738,7 +14752,7 @@
         <v>PENDING</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="36"/>
@@ -14747,7 +14761,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -14756,16 +14770,16 @@
         <v>209</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="H9" s="41"/>
       <c r="I9" s="31" t="str">
@@ -14773,7 +14787,7 @@
         <v>PENDING</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="36"/>
@@ -14782,25 +14796,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="31" t="str">
@@ -14808,7 +14822,7 @@
         <v>PENDING</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="36"/>
@@ -14817,25 +14831,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="31" t="str">
@@ -14843,7 +14857,7 @@
         <v>PENDING</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="36"/>
@@ -14852,25 +14866,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F12" s="40" t="n">
         <v>10000</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="31" t="str">
@@ -14878,7 +14892,7 @@
         <v>PENDING</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K12" s="33"/>
       <c r="L12" s="36"/>
@@ -14887,7 +14901,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>7</v>
@@ -14896,16 +14910,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F13" s="40" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="31" t="str">
@@ -14913,7 +14927,7 @@
         <v>PENDING</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="36"/>
@@ -14922,7 +14936,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>7</v>
@@ -14931,16 +14945,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="31" t="str">
@@ -14948,7 +14962,7 @@
         <v>PENDING</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="36"/>
@@ -14957,25 +14971,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>0.001</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="31" t="str">
@@ -14983,7 +14997,7 @@
         <v>PENDING</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K15" s="33"/>
       <c r="L15" s="36"/>
@@ -14992,25 +15006,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="31" t="str">
@@ -15018,7 +15032,7 @@
         <v>PENDING</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="36"/>
@@ -15027,25 +15041,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="31" t="str">
@@ -15053,7 +15067,7 @@
         <v>PENDING</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="36"/>
@@ -15062,25 +15076,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="31" t="str">
@@ -15088,7 +15102,7 @@
         <v>PENDING</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="36"/>
@@ -15097,7 +15111,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -15106,16 +15120,16 @@
         <v>42</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="31" t="str">
@@ -15123,7 +15137,7 @@
         <v>PENDING</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="36"/>
@@ -15132,25 +15146,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>15</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="31" t="str">
@@ -15158,7 +15172,7 @@
         <v>PENDING</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
@@ -15167,25 +15181,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="31" t="str">
@@ -15193,7 +15207,7 @@
         <v>PENDING</v>
       </c>
       <c r="J21" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="36"/>
@@ -15202,25 +15216,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0.75</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="31" t="str">
@@ -15228,7 +15242,7 @@
         <v>PENDING</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="36"/>
@@ -15237,25 +15251,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>0.9995</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H23" s="39"/>
       <c r="I23" s="31" t="str">
@@ -15263,7 +15277,7 @@
         <v>PENDING</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="36"/>
@@ -15334,7 +15348,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -15343,69 +15357,69 @@
         <v>88</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="W1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -15414,13 +15428,13 @@
         <v>114</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G2" s="28" t="n">
         <v>30</v>
@@ -15470,15 +15484,15 @@
         <v>46338</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -15487,13 +15501,13 @@
         <v>114</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>15</v>
@@ -15529,7 +15543,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -15538,13 +15552,13 @@
         <v>116</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G4" s="31" t="n">
         <v>5</v>
@@ -15580,7 +15594,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
@@ -15589,13 +15603,13 @@
         <v>114</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>30</v>
@@ -15631,7 +15645,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
@@ -15640,13 +15654,13 @@
         <v>115</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>30</v>
@@ -15682,7 +15696,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
@@ -15691,13 +15705,13 @@
         <v>116</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>5</v>
@@ -15733,7 +15747,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
@@ -15742,13 +15756,13 @@
         <v>117</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>480</v>
@@ -15784,7 +15798,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -15793,13 +15807,13 @@
         <v>118</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G9" s="31" t="n">
         <v>30</v>
@@ -15835,7 +15849,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>7</v>
@@ -15844,13 +15858,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G10" s="31" t="n">
         <v>15</v>
@@ -15937,72 +15951,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="I2" s="28" t="n">
         <v>12</v>
@@ -16011,7 +16025,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46340</v>
@@ -16021,30 +16035,30 @@
         <v>PASS</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
@@ -16061,25 +16075,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
@@ -16096,25 +16110,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
@@ -16131,25 +16145,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
@@ -16166,25 +16180,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -16201,25 +16215,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
@@ -16236,25 +16250,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -16327,40 +16341,40 @@
         <v>140</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16368,13 +16382,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E2" s="30" t="n">
         <v>0.93</v>
@@ -16402,7 +16416,7 @@
         <v>46346</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16410,13 +16424,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="31" t="s">
+        <v>976</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>973</v>
+      </c>
+      <c r="D3" s="31" t="s">
         <v>974</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>971</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>972</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
@@ -16442,13 +16456,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -16474,13 +16488,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -16506,13 +16520,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -16538,13 +16552,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16570,13 +16584,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="1025">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -735,7 +735,7 @@
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40006549728</t>
   </si>
   <si>
-    <t xml:space="preserve">First service image through the full pipeline on main (run 40006549728): Java tests gate the image; Trivy CRITICAL gate passed (0 fixable; 1 unfixed CRITICAL in the distroless Debian 13 base, libbrotli1 CVE-2026-111497, tracked until a patched base ships); SPDX SBOM; multi-arch push to GHCR; keyless cosign signature and SBOM attestation verified with cosign verify against the container.yml@refs/heads/main identity (and rejected for any other identity). PR pipeline: 3.3 min; image job 2m43s on PRs, 8m12s on main (multi-arch). Earlier: ci.yml, Terraform plan/apply via OIDC, SHA-pinned actions, Dependabot, ADR-0003.</t>
+    <t xml:space="preserve">First service image through the full pipeline on main (run 40006549728): Java tests gate the image; Trivy CRITICAL gate passed (0 fixable; 1 unfixed CRITICAL in the distroless Debian 13 base, libbrotli1 CVE-2026-111497, tracked until a patched base ships); SPDX SBOM; multi-arch push to GHCR; keyless cosign signature and SBOM attestation verified with cosign verify against the container.yml@refs/heads/main identity (and rejected for any other identity). PR pipeline: 3.3 min; image job 2m43s on PRs, 8m12s on main (multi-arch). Earlier: ci.yml, Terraform plan/apply via OIDC, SHA-pinned actions, Dependabot, ADR-0003. | 2026-10-25: SAST (CodeQL, Semgrep) and linters (SpotBugs, ruff, ShellCheck) added (TC-PLT-005/013); images also carry classic signatures for admission.</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T06</t>
@@ -750,7 +750,7 @@
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/39993278414</t>
   </si>
   <si>
-    <t xml:space="preserve">Real EKS dev cycle from main: apply 12m20s (101 resources), 60/60 checks passed in 4m05s, destroy 12m05s with 0 left. Terraform installs ArgoCD and one root per environment; ArgoCD deploys ESO, the secret store and the services ApplicationSet from Git. Secrets Manager values reach pods in meterbook-dev and meterbook-staging via Pod Identity; smoke service hardened; VPC CNI enforces NetworkPolicy. Every PR: ArgoCD on kind syncs dev+staging at the commit under test, 18/18 incl. staging self-heal (CI run 39991279763). Library chart with guard rails (38 render tests), GitOps policy check, prod pinned by SHA via scripts/promote-prod.sh, ADR-0006, runbook. Fixed on the way: podinfo command/args, ECR Public pull limits (Redis from mirror.gcr.io by digest), account ID masked in public logs. Evidence: docs/evidence/2026-10-23-dev-gitops-eks.md</t>
+    <t xml:space="preserve">Real EKS dev cycle from main: apply 12m20s (101 resources), 60/60 checks passed in 4m05s, destroy 12m05s with 0 left. Terraform installs ArgoCD and one root per environment; ArgoCD deploys ESO, the secret store and the services ApplicationSet from Git. Secrets Manager values reach pods in meterbook-dev and meterbook-staging via Pod Identity; smoke service hardened; VPC CNI enforces NetworkPolicy. Every PR: ArgoCD on kind syncs dev+staging at the commit under test, 18/18 incl. staging self-heal (CI run 39991279763). Library chart with guard rails (38 render tests), GitOps policy check, prod pinned by SHA via scripts/promote-prod.sh, ADR-0006, runbook. Fixed on the way: podinfo command/args, ECR Public pull limits (Redis from mirror.gcr.io by digest), account ID masked in public logs. Evidence: docs/evidence/2026-10-23-dev-gitops-eks.md | 2026-10-25: admission verifies signatures (ADR-0012, policy-controller); prod has identity, mesh, smoke and image policy, promoted; prod e2e on kind in CI.</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T07</t>
@@ -768,7 +768,7 @@
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40065555690</t>
   </si>
   <si>
-    <t xml:space="preserve">DoD: SSO e2e in a real browser through a SAML IdP passes in CI on every identity change (TC-PLT-001; run 40065295770): tenant, SAML connection, SCIM token and user set up through the APIs; SSO sign-in lands in the tenant; JIT users join the tenant; another tenant's IdP asserting a victim's email is refused; SCIM deactivation kills the session and blocks sign-in. On EKS (run 40065555690): Keycloak + identity per environment via ArgoCD, db-bootstrap, operator creates a tenant, RDS isolation; 78/78 checks, 107 resources applied and destroyed. Built: ADR-0007/0008, design doc, OpenAPI contract with Spectral + oasdiff in CI, Spring Boot 4.1 on Java 25, Keycloak adapter, tenants, SAML SSO connections, SCIM 2.0 Users/Groups, Idempotency-Key, 158 tests (97% line / 87% branch). Found and fixed: cross-tenant account takeover via link-by-email; SCIM secret in idempotency store; Keycloak 26.8 domain routing; JIT onboarding; ArgoCD subchart dependency; a false-green CI pipeline (pipefail). Evidence: docs/evidence/2026-10-24-identity-sso-and-eks.md</t>
+    <t xml:space="preserve">DoD: SSO e2e in a real browser through a SAML IdP passes in CI on every identity change (TC-PLT-001; run 40065295770): tenant, SAML connection, SCIM token and user set up through the APIs; SSO sign-in lands in the tenant; JIT users join the tenant; another tenant's IdP asserting a victim's email is refused; SCIM deactivation kills the session and blocks sign-in. On EKS (run 40065555690): Keycloak + identity per environment via ArgoCD, db-bootstrap, operator creates a tenant, RDS isolation; 78/78 checks, 107 resources applied and destroyed. Built: ADR-0007/0008, design doc, OpenAPI contract with Spectral + oasdiff in CI, Spring Boot 4.1 on Java 25, Keycloak adapter, tenants, SAML SSO connections, SCIM 2.0 Users/Groups, Idempotency-Key, 158 tests (97% line / 87% branch). Found and fixed: cross-tenant account takeover via link-by-email; SCIM secret in idempotency store; Keycloak 26.8 domain routing; JIT onboarding; ArgoCD subchart dependency; a false-green CI pipeline (pipefail). Evidence: docs/evidence/2026-10-24-identity-sso-and-eks.md | 2026-10-25: Keycloak and identity run 2 replicas with PDBs in prod and dev; Keycloak clustering verified on EKS.</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T08</t>
@@ -804,7 +804,7 @@
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40085243536</t>
   </si>
   <si>
-    <t xml:space="preserve">DoD: a revoked key is rejected on the very next request by identity (API test and browser e2e with a real Keycloak tenant admin, CI run 40084140187); other services may cache a verification for at most 30 s (Cache-Control: max-age=30; refusals no-store), so every service rejects it within 30 s. On EKS (run 40085243536): 87/87 checks, 107 resources applied and destroyed; /v1/api-key refuses no credentials, unknown keys and access tokens with no-store; V6 on RDS under forced RLS. Built: ADR-0010; keys mb_live_/mb_test_ + 238 random bits + CRC-32, SHA-256 at rest, shown once, never in idempotency records; one environment per key; scopes from a fixed vocabulary; expiry; rotation with a grace period; immediate revocation; 50 live keys per environment; last_used_at; keys cannot call the admin API. 193 tests (97.5% line / 87.1% branch). Found and fixed: timestamps serialised in the JVM zone instead of UTC; 500 for a non-key authentication on /v1/api-key; expired keys counting toward the limit; jOOQ self-reference clash. Evidence: docs/evidence/2026-10-24-api-keys.md</t>
+    <t xml:space="preserve">DoD: a revoked key is rejected on the very next request by identity (API test and browser e2e with a real Keycloak tenant admin, CI run 40084140187); other services may cache a verification for at most 30 s (Cache-Control: max-age=30; refusals no-store), so every service rejects it within 30 s. On EKS (run 40085243536): 87/87 checks, 107 resources applied and destroyed; /v1/api-key refuses no credentials, unknown keys and access tokens with no-store; V6 on RDS under forced RLS. Built: ADR-0010; keys mb_live_/mb_test_ + 238 random bits + CRC-32, SHA-256 at rest, shown once, never in idempotency records; one environment per key; scopes from a fixed vocabulary; expiry; rotation with a grace period; immediate revocation; 50 live keys per environment; last_used_at; keys cannot call the admin API. 193 tests (97.5% line / 87.1% branch). Found and fixed: timestamps serialised in the JVM zone instead of UTC; 500 for a non-key authentication on /v1/api-key; expired keys counting toward the limit; jOOQ self-reference clash. Evidence: docs/evidence/2026-10-24-api-keys.md | 2026-10-25: a real tenant admin signs in on EKS (PKCE) and a revoked key is rejected there.</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T10</t>
@@ -819,7 +819,7 @@
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40091917398</t>
   </si>
   <si>
-    <t xml:space="preserve">DoD: plaintext pod-to-pod traffic is rejected. A pod outside the mesh, in the same namespace (admitted by the NetworkPolicy), is refused by strict mTLS; ztunnel logs 'explicitly denied by: istio-system/istio_converted_static_strict', asserted in the GitOps e2e on kind (CI run 40089193779, 34/34) and on EKS (run 40091917398: 107/107, 107 resources applied and destroyed). Control experiment: PERMISSIVE let the same plaintext pod through, STRICT refused it. In-mesh traffic carries SPIFFE identities, incl. identity -&gt; Keycloak as spiffe://cluster.local/ns/meterbook-dev/sa/identity. Built: ADR-0011 (Linkerd vs Istio sidecars vs Istio ambient); Istio 1.31.3 ambient via ArgoCD (charts from ghcr.io OCI, images from mirror.gcr.io); platform-mesh chart (STRICT, namespace enrolment from Git, never pruned); NetworkPolicies admit HBONE 15008 and mesh probe address only; render tests. Found and fixed: Istio 1.31 left gcr.io; ambient needs 15008 and 169.254.7.127 in NetworkPolicies; in-cluster verification lost output (kubectl run -i race), now run to completion and read from logs. Prod gets the mesh with its environment. Evidence: docs/evidence/2026-10-24-service-mesh-mtls.md</t>
+    <t xml:space="preserve">DoD: plaintext pod-to-pod traffic is rejected. A pod outside the mesh, in the same namespace (admitted by the NetworkPolicy), is refused by strict mTLS; ztunnel logs 'explicitly denied by: istio-system/istio_converted_static_strict', asserted in the GitOps e2e on kind (CI run 40089193779, 34/34) and on EKS (run 40091917398: 107/107, 107 resources applied and destroyed). Control experiment: PERMISSIVE let the same plaintext pod through, STRICT refused it. In-mesh traffic carries SPIFFE identities, incl. identity -&gt; Keycloak as spiffe://cluster.local/ns/meterbook-dev/sa/identity. Built: ADR-0011 (Linkerd vs Istio sidecars vs Istio ambient); Istio 1.31.3 ambient via ArgoCD (charts from ghcr.io OCI, images from mirror.gcr.io); platform-mesh chart (STRICT, namespace enrolment from Git, never pruned); NetworkPolicies admit HBONE 15008 and mesh probe address only; render tests. Found and fixed: Istio 1.31 left gcr.io; ambient needs 15008 and 169.254.7.127 in NetworkPolicies; in-cluster verification lost output (kubectl run -i race), now run to completion and read from logs. Prod gets the mesh with its environment. Evidence: docs/evidence/2026-10-24-service-mesh-mtls.md | 2026-10-25: TC-PLT-020 added; mTLS identities proven from ztunnel metrics; prod gets the mesh.</t>
   </si>
   <si>
     <t xml:space="preserve">MB-T11</t>
@@ -2043,6 +2043,12 @@
     <t xml:space="preserve">0 high/critical findings</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeQL (security-extended; Java, Python, Actions) on every PR, main and weekly: 0 high/critical (a finding &gt;= 7.0 fails the run); Semgrep p/default on every change: 0 errors/warnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40122321805</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-PLT-006</t>
   </si>
   <si>
@@ -2052,7 +2058,10 @@
     <t xml:space="preserve">Trivy</t>
   </si>
   <si>
-    <t xml:space="preserve">0 fixable CRITICAL in meterbook-identity; 1 unfixed CRITICAL in the distroless base (libbrotli1 CVE-2026-111497), tracked</t>
+    <t xml:space="preserve">0 CRITICAL, including unfixed, in all 4 deployed images (identity, Keycloak, db-bootstrap, smoke; Trivy 0.76.1, OS packages, jars, Go binaries); CI fails on fixable CRITICAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40115148732</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-007</t>
@@ -2142,6 +2151,12 @@
     <t xml:space="preserve">Linters in CI</t>
   </si>
   <si>
+    <t xml:space="preserve">This repo has Java, Python and shell (no Go or Rust): SpotBugs in ./gradlew check (found and fixed 5 real bugs; any finding fails), ruff and ShellCheck on every change; ci requires the job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40122321801</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-PLT-014</t>
   </si>
   <si>
@@ -2523,6 +2538,42 @@
     <t xml:space="preserve">Custom generator</t>
   </si>
   <si>
+    <t xml:space="preserve">TC-PLT-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service mesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaintext request from a pod outside the mesh to a meshed service in the same namespace (NetworkPolicy admits it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused by strict mTLS (ztunnel names the strict policy); in-mesh calls carry SPIFFE identities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind e2e + EKS verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused with "explicitly denied by istio-system/istio_converted_static_strict"; PERMISSIVE control let the same pod through; identity -&gt; Keycloak counted as mutual_tls from spiffe://cluster.local/ns/meterbook-dev/sa/identity (EKS 123/123)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40117597732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-PLT-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy an image not signed by container.yml on main into an application namespace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refused at admission; every pinned image admitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsigned busybox refused ("no matching policies") in meterbook-*, allowed outside; all 4 pinned images pass a server-side dry run through the policy (EKS 123/123)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metric ID</t>
   </si>
   <si>
@@ -2649,6 +2700,15 @@
     <t xml:space="preserve">count</t>
   </si>
   <si>
+    <t xml:space="preserve">Trivy 0.76.1 on the 4 pinned images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/evidence/2026-10-25-baseline-gaps.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL including unfixed; CI blocks fixable CRITICAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">M-PLT-08</t>
   </si>
   <si>
@@ -3094,6 +3154,9 @@
   </si>
   <si>
     <t xml:space="preserve">identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40120018649</t>
   </si>
   <si>
     <t xml:space="preserve">tenancy</t>
@@ -4281,54 +4344,54 @@
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>981</v>
+        <v>1002</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>982</v>
+        <v>1003</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>983</v>
+        <v>1004</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>990</v>
+        <v>1011</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4341,10 +4404,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>993</v>
+        <v>1014</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="L2" s="28" t="s">
         <v>599</v>
@@ -6101,31 +6164,31 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1002</v>
+        <v>1023</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>594</v>
@@ -6755,7 +6818,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">COUNTIF(Test_Cases!$B$2:$B$600,B$4)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF(Test_Cases!$B$2:$B$600,C$4)</f>
@@ -6763,7 +6826,7 @@
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">SUM(B17:C17)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6772,7 +6835,7 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Pass")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Pass")</f>
@@ -6780,7 +6843,7 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">SUM(B18:C18)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6823,7 +6886,7 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,B$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$B$2:$B$600,C$4,Test_Cases!$K$2:$K$600,"Not Run")</f>
@@ -6831,7 +6894,7 @@
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">SUM(B21:C21)</f>
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6840,7 +6903,7 @@
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IFERROR((B17-B21)/B17,0)</f>
-        <v>0.315789473684211</v>
+        <v>0.476190476190476</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">IFERROR((C17-C21)/C17,0)</f>
@@ -6848,7 +6911,7 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">IFERROR((D17-D21)/D17,0)</f>
-        <v>0.133333333333333</v>
+        <v>0.212765957446809</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6916,7 +6979,7 @@
       </c>
       <c r="B28" s="18" t="n">
         <f aca="false">COUNTIFS(Metrics_SLOs!$B$2:$B$600,B$4,Metrics_SLOs!$I$2:$I$600,"PASS")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIFS(Metrics_SLOs!$B$2:$B$600,C$4,Metrics_SLOs!$I$2:$I$600,"PASS")</f>
@@ -6924,7 +6987,7 @@
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">SUM(B28:C28)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6950,7 +7013,7 @@
       </c>
       <c r="B30" s="18" t="n">
         <f aca="false">COUNTIFS(Metrics_SLOs!$B$2:$B$600,B$4,Metrics_SLOs!$I$2:$I$600,"PENDING")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIFS(Metrics_SLOs!$B$2:$B$600,C$4,Metrics_SLOs!$I$2:$I$600,"PENDING")</f>
@@ -6958,7 +7021,7 @@
       </c>
       <c r="D30" s="19" t="n">
         <f aca="false">SUM(B30:C30)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7035,7 +7098,7 @@
       </c>
       <c r="B35" s="23" t="str">
         <f aca="false">COUNTIFS(Coverage!$A$2:$A$600,B$4,Coverage!$K$2:$K$600,"PASS")&amp;" / "&amp;COUNTIF(Coverage!$A$2:$A$600,B$4)</f>
-        <v>0 / 2</v>
+        <v>2 / 2</v>
       </c>
       <c r="C35" s="23" t="str">
         <f aca="false">COUNTIFS(Coverage!$A$2:$A$600,C$4,Coverage!$K$2:$K$600,"PASS")&amp;" / "&amp;COUNTIF(Coverage!$A$2:$A$600,C$4)</f>
@@ -7043,7 +7106,7 @@
       </c>
       <c r="D35" s="23" t="str">
         <f aca="false">(COUNTIF(Coverage!$K$2:$K$600,"PASS")-COUNTIFS(Coverage!$A$2:$A$600,"EXAMPLE",Coverage!$K$2:$K$600,"PASS"))&amp;" / "&amp;(COUNTA(Coverage!$A$2:$A$600)-COUNTIF(Coverage!$A$2:$A$600,"EXAMPLE"))</f>
-        <v>0 / 6</v>
+        <v>2 / 6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7502,7 +7565,7 @@
       </c>
       <c r="D60" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -7510,7 +7573,7 @@
       </c>
       <c r="F60" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Not Run")-COUNTIFS(Test_Cases!$C$2:$C$600,A60,Test_Cases!$K$2:$K$600,"Not Run",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8052,7 +8115,7 @@
       </c>
       <c r="D82" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -8060,7 +8123,7 @@
       </c>
       <c r="F82" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Not Run")-COUNTIFS(Test_Cases!$C$2:$C$600,A82,Test_Cases!$K$2:$K$600,"Not Run",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8073,11 +8136,11 @@
       </c>
       <c r="C83" s="27" t="n">
         <f aca="false">COUNTIF(Test_Cases!$C$2:$C$600,A83)-COUNTIFS(Test_Cases!$C$2:$C$600,A83,Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A83,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A83,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A83,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A83,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -8148,11 +8211,11 @@
       </c>
       <c r="C86" s="27" t="n">
         <f aca="false">COUNTIF(Test_Cases!$C$2:$C$600,A86)-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Pass")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Pass",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="27" t="n">
         <f aca="false">COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Fail")-COUNTIFS(Test_Cases!$C$2:$C$600,A86,Test_Cases!$K$2:$K$600,"Fail",Test_Cases!$B$2:$B$600,"EXAMPLE")</f>
@@ -8339,7 +8402,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71B98949-D6D7-44F3-8360-3118E843C836}</x14:id>
+          <x14:id>{335289DB-DB61-408A-87EF-B07A376756B3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8353,7 +8416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8219F0EC-4BDA-43B7-A77C-E3E6C200ADEE}</x14:id>
+          <x14:id>{C979CEB7-F435-4329-AD6E-5EECE5235CCE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8367,7 +8430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D6F31996-A280-40E7-B386-25F134B1DBE6}</x14:id>
+          <x14:id>{14D6A86A-A5CA-43DB-BABA-C785A5B749CE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8381,7 +8444,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{607D3F38-9D15-4585-835C-6AD750874E71}</x14:id>
+          <x14:id>{86D04ABD-1823-45B5-A3D3-DA6F2BA3C52F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8427,7 +8490,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71B98949-D6D7-44F3-8360-3118E843C836}">
+          <x14:cfRule type="dataBar" id="{335289DB-DB61-408A-87EF-B07A376756B3}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8442,7 +8505,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8219F0EC-4BDA-43B7-A77C-E3E6C200ADEE}">
+          <x14:cfRule type="dataBar" id="{C979CEB7-F435-4329-AD6E-5EECE5235CCE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8457,7 +8520,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D6F31996-A280-40E7-B386-25F134B1DBE6}">
+          <x14:cfRule type="dataBar" id="{14D6A86A-A5CA-43DB-BABA-C785A5B749CE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8472,7 +8535,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{607D3F38-9D15-4585-835C-6AD750874E71}">
+          <x14:cfRule type="dataBar" id="{86D04ABD-1823-45B5-A3D3-DA6F2BA3C52F}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10655,7 +10718,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F69AD8A5-E010-4990-B3A8-E2E633EE8FBA}</x14:id>
+          <x14:id>{A4B27AF6-B282-44F5-988D-F9DA739DB031}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10686,7 +10749,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F69AD8A5-E010-4990-B3A8-E2E633EE8FBA}">
+          <x14:cfRule type="dataBar" id="{A4B27AF6-B282-44F5-988D-F9DA739DB031}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12438,7 +12501,7 @@
     <tabColor rgb="FF548235"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -12762,16 +12825,22 @@
         <v>599</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="33"/>
+        <v>378</v>
+      </c>
+      <c r="L7" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M7" s="33" t="s">
+        <v>626</v>
+      </c>
       <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
+      <c r="O7" s="33" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
@@ -12787,13 +12856,13 @@
         <v>623</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G8" s="31" t="s">
         <v>543</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>161</v>
@@ -12805,19 +12874,19 @@
         <v>378</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N8" s="33"/>
       <c r="O8" s="33" t="s">
-        <v>189</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -12833,7 +12902,7 @@
         <v>623</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>547</v>
@@ -12854,16 +12923,16 @@
         <v>46318</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N9" s="33"/>
       <c r="O9" s="33" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
@@ -12876,10 +12945,10 @@
         <v>Black</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="G10" s="31" t="s">
         <v>551</v>
@@ -12903,7 +12972,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
@@ -12916,13 +12985,13 @@
         <v>Black</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H11" s="31" t="s">
         <v>372</v>
@@ -12943,7 +13012,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>5</v>
@@ -12956,16 +13025,16 @@
         <v>Grey</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>161</v>
@@ -12983,7 +13052,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>5</v>
@@ -12996,13 +13065,13 @@
         <v>Grey</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>554</v>
@@ -13023,7 +13092,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>5</v>
@@ -13036,16 +13105,16 @@
         <v>Grey</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="I14" s="31" t="s">
         <v>161</v>
@@ -13063,7 +13132,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>5</v>
@@ -13079,13 +13148,13 @@
         <v>623</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="I15" s="31" t="s">
         <v>161</v>
@@ -13094,16 +13163,22 @@
         <v>599</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="36"/>
-      <c r="M15" s="33"/>
+        <v>378</v>
+      </c>
+      <c r="L15" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>662</v>
+      </c>
       <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
+      <c r="O15" s="33" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>5</v>
@@ -13119,13 +13194,13 @@
         <v>623</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>161</v>
@@ -13140,7 +13215,7 @@
         <v>46319</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="N16" s="33"/>
       <c r="O16" s="33" t="s">
@@ -13149,7 +13224,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>5</v>
@@ -13162,16 +13237,16 @@
         <v>Black</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="I17" s="31" t="s">
         <v>168</v>
@@ -13189,7 +13264,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>5</v>
@@ -13202,13 +13277,13 @@
         <v>Grey</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="H18" s="31" t="s">
         <v>509</v>
@@ -13229,7 +13304,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>5</v>
@@ -13242,16 +13317,16 @@
         <v>Grey</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="I19" s="31" t="s">
         <v>168</v>
@@ -13269,7 +13344,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>5</v>
@@ -13285,13 +13360,13 @@
         <v>5</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="I20" s="31" t="s">
         <v>238</v>
@@ -13309,7 +13384,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>5</v>
@@ -13322,10 +13397,10 @@
         <v>Black</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="G21" s="31" t="s">
         <v>559</v>
@@ -13349,7 +13424,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
@@ -13362,16 +13437,16 @@
         <v>White</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="I22" s="31" t="s">
         <v>161</v>
@@ -13389,7 +13464,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
@@ -13402,13 +13477,13 @@
         <v>White</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="H23" s="31" t="s">
         <v>421</v>
@@ -13429,7 +13504,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>7</v>
@@ -13442,16 +13517,16 @@
         <v>White</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="I24" s="31" t="s">
         <v>168</v>
@@ -13469,7 +13544,7 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>7</v>
@@ -13482,13 +13557,13 @@
         <v>Black</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>351</v>
@@ -13509,7 +13584,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B26" s="31" t="s">
         <v>7</v>
@@ -13525,10 +13600,10 @@
         <v>596</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H26" s="31" t="s">
         <v>442</v>
@@ -13549,7 +13624,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>7</v>
@@ -13562,16 +13637,16 @@
         <v>White</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="I27" s="31" t="s">
         <v>161</v>
@@ -13589,7 +13664,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="31" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>7</v>
@@ -13602,13 +13677,13 @@
         <v>Black</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="H28" s="31" t="s">
         <v>344</v>
@@ -13629,7 +13704,7 @@
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>7</v>
@@ -13642,16 +13717,16 @@
         <v>Grey</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G29" s="31" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="I29" s="31" t="s">
         <v>161</v>
@@ -13669,7 +13744,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B30" s="31" t="s">
         <v>7</v>
@@ -13682,16 +13757,16 @@
         <v>Black</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="G30" s="31" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="I30" s="31" t="s">
         <v>161</v>
@@ -13709,7 +13784,7 @@
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>7</v>
@@ -13722,13 +13797,13 @@
         <v>Black</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="G31" s="31" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="H31" s="31" t="s">
         <v>391</v>
@@ -13749,7 +13824,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B32" s="31" t="s">
         <v>7</v>
@@ -13762,13 +13837,13 @@
         <v>White</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="H32" s="31" t="s">
         <v>429</v>
@@ -13789,7 +13864,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="31" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>7</v>
@@ -13802,13 +13877,13 @@
         <v>Black</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="G33" s="31" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>366</v>
@@ -13829,7 +13904,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B34" s="31" t="s">
         <v>7</v>
@@ -13842,16 +13917,16 @@
         <v>Grey</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="I34" s="31" t="s">
         <v>161</v>
@@ -13869,7 +13944,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>7</v>
@@ -13882,13 +13957,13 @@
         <v>Black</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="H35" s="31" t="s">
         <v>554</v>
@@ -13909,7 +13984,7 @@
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="31" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>7</v>
@@ -13922,13 +13997,13 @@
         <v>Grey</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="H36" s="31" t="s">
         <v>451</v>
@@ -13949,7 +14024,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>7</v>
@@ -13962,10 +14037,10 @@
         <v>Black</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="G37" s="31" t="s">
         <v>388</v>
@@ -13989,7 +14064,7 @@
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="31" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>7</v>
@@ -14002,16 +14077,16 @@
         <v>Grey</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="I38" s="31" t="s">
         <v>161</v>
@@ -14029,7 +14104,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>7</v>
@@ -14042,13 +14117,13 @@
         <v>Black</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="H39" s="31" t="s">
         <v>353</v>
@@ -14069,7 +14144,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>7</v>
@@ -14082,13 +14157,13 @@
         <v>Black</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="H40" s="31" t="s">
         <v>572</v>
@@ -14109,7 +14184,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>7</v>
@@ -14122,16 +14197,16 @@
         <v>Black</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="I41" s="31" t="s">
         <v>168</v>
@@ -14149,7 +14224,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>7</v>
@@ -14162,13 +14237,13 @@
         <v>Black</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="H42" s="31" t="s">
         <v>470</v>
@@ -14189,7 +14264,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="31" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>7</v>
@@ -14202,13 +14277,13 @@
         <v>Black</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="G43" s="31" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="H43" s="31" t="s">
         <v>470</v>
@@ -14229,7 +14304,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>7</v>
@@ -14242,13 +14317,13 @@
         <v>Black</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="G44" s="31" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="H44" s="31" t="s">
         <v>470</v>
@@ -14269,7 +14344,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
@@ -14282,13 +14357,13 @@
         <v>Black</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="G45" s="31" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="H45" s="31" t="s">
         <v>483</v>
@@ -14309,7 +14384,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>7</v>
@@ -14322,13 +14397,13 @@
         <v>Black</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="H46" s="31" t="s">
         <v>470</v>
@@ -14349,7 +14424,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="31" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>7</v>
@@ -14362,16 +14437,16 @@
         <v>Black</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="I47" s="31" t="s">
         <v>168</v>
@@ -14386,6 +14461,98 @@
       <c r="M47" s="33"/>
       <c r="N47" s="33"/>
       <c r="O47" s="33"/>
+    </row>
+    <row r="48" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="31" t="s">
+        <v>791</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(Test_Catalog!$C$2:$C$48,MATCH(C48,Test_Catalog!$A$2:$A$48,0)),"")</f>
+        <v>Black</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>792</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>793</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>794</v>
+      </c>
+      <c r="H48" s="31" t="s">
+        <v>795</v>
+      </c>
+      <c r="I48" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="K48" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="L48" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M48" s="33" t="s">
+        <v>796</v>
+      </c>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="31" t="s">
+        <v>798</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="31" t="str">
+        <f aca="false">IFERROR(INDEX(Test_Catalog!$C$2:$C$48,MATCH(C49,Test_Catalog!$A$2:$A$48,0)),"")</f>
+        <v>White</v>
+      </c>
+      <c r="E49" s="31" t="s">
+        <v>799</v>
+      </c>
+      <c r="F49" s="31" t="s">
+        <v>800</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>801</v>
+      </c>
+      <c r="H49" s="31" t="s">
+        <v>795</v>
+      </c>
+      <c r="I49" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="K49" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="L49" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M49" s="33" t="s">
+        <v>802</v>
+      </c>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33" t="s">
+        <v>797</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O600"/>
@@ -14454,7 +14621,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>786</v>
+        <v>803</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -14463,31 +14630,31 @@
         <v>310</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="M1" s="13" t="s">
         <v>594</v>
@@ -14498,7 +14665,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -14507,16 +14674,16 @@
         <v>42</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F2" s="37" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="H2" s="37" t="n">
         <v>38</v>
@@ -14529,37 +14696,37 @@
         <v>470</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46338</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="N2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F3" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H3" s="39"/>
       <c r="I3" s="31" t="str">
@@ -14567,7 +14734,7 @@
         <v>PENDING</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="36"/>
@@ -14576,7 +14743,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -14585,16 +14752,16 @@
         <v>42</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F4" s="40" t="n">
         <v>300</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="31" t="str">
@@ -14611,25 +14778,25 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>811</v>
+        <v>828</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F5" s="40" t="n">
         <v>10</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H5" s="41" t="n">
         <v>3.3</v>
@@ -14639,42 +14806,42 @@
         <v>PASS</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="L5" s="36" t="n">
         <v>46318</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F6" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>818</v>
+        <v>835</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="31" t="str">
@@ -14682,7 +14849,7 @@
         <v>PENDING</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>819</v>
+        <v>836</v>
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="36"/>
@@ -14691,25 +14858,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>820</v>
+        <v>837</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F7" s="38" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H7" s="39"/>
       <c r="I7" s="31" t="str">
@@ -14717,7 +14884,7 @@
         <v>PENDING</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="36"/>
@@ -14726,25 +14893,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>823</v>
+        <v>840</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>824</v>
+        <v>841</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F8" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H8" s="41"/>
       <c r="I8" s="31" t="str">
@@ -14752,7 +14919,7 @@
         <v>PENDING</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="36"/>
@@ -14761,7 +14928,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>825</v>
+        <v>842</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>5</v>
@@ -14770,51 +14937,61 @@
         <v>209</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>827</v>
-      </c>
-      <c r="H9" s="41"/>
+        <v>844</v>
+      </c>
+      <c r="H9" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="31" t="str">
         <f aca="false">IF(H9="","PENDING",IF(E9="&lt;=",IF(H9&lt;=F9,"PASS","FAIL"),IF(H9&gt;=F9,"PASS","FAIL")))</f>
-        <v>PENDING</v>
+        <v>PASS</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>628</v>
-      </c>
-      <c r="K9" s="33"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
+        <v>630</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>845</v>
+      </c>
+      <c r="L9" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>846</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="31" t="str">
@@ -14822,7 +14999,7 @@
         <v>PENDING</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="36"/>
@@ -14831,25 +15008,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="31" t="str">
@@ -14857,7 +15034,7 @@
         <v>PENDING</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="36"/>
@@ -14866,25 +15043,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="B12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F12" s="40" t="n">
         <v>10000</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="31" t="str">
@@ -14901,7 +15078,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="31" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>7</v>
@@ -14910,16 +15087,16 @@
         <v>42</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F13" s="40" t="n">
         <v>25</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="H13" s="41"/>
       <c r="I13" s="31" t="str">
@@ -14936,7 +15113,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="B14" s="31" t="s">
         <v>7</v>
@@ -14945,16 +15122,16 @@
         <v>42</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="H14" s="41"/>
       <c r="I14" s="31" t="str">
@@ -14971,25 +15148,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F15" s="38" t="n">
         <v>0.001</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="31" t="str">
@@ -15006,25 +15183,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="31" t="str">
@@ -15032,7 +15209,7 @@
         <v>PENDING</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="K16" s="33"/>
       <c r="L16" s="36"/>
@@ -15041,25 +15218,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="31" t="str">
@@ -15067,7 +15244,7 @@
         <v>PENDING</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="36"/>
@@ -15076,25 +15253,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F18" s="38" t="n">
         <v>0.999</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="31" t="str">
@@ -15102,7 +15279,7 @@
         <v>PENDING</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="36"/>
@@ -15111,7 +15288,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>7</v>
@@ -15120,16 +15297,16 @@
         <v>42</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F19" s="40" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="31" t="str">
@@ -15137,7 +15314,7 @@
         <v>PENDING</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="36"/>
@@ -15146,25 +15323,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F20" s="40" t="n">
         <v>15</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H20" s="41"/>
       <c r="I20" s="31" t="str">
@@ -15172,7 +15349,7 @@
         <v>PENDING</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
@@ -15181,25 +15358,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F21" s="38" t="n">
         <v>0.9</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H21" s="39"/>
       <c r="I21" s="31" t="str">
@@ -15216,25 +15393,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
       <c r="B22" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F22" s="38" t="n">
         <v>0.75</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H22" s="39"/>
       <c r="I22" s="31" t="str">
@@ -15242,7 +15419,7 @@
         <v>PENDING</v>
       </c>
       <c r="J22" s="31" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="36"/>
@@ -15251,25 +15428,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>0.9995</v>
       </c>
       <c r="G23" s="31" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
       <c r="H23" s="39"/>
       <c r="I23" s="31" t="str">
@@ -15277,7 +15454,7 @@
         <v>PENDING</v>
       </c>
       <c r="J23" s="31" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="K23" s="33"/>
       <c r="L23" s="36"/>
@@ -15348,7 +15525,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
@@ -15363,55 +15540,55 @@
         <v>589</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="V1" s="13" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="W1" s="13" t="s">
         <v>594</v>
@@ -15419,7 +15596,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
@@ -15428,13 +15605,13 @@
         <v>114</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>470</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G2" s="28" t="n">
         <v>30</v>
@@ -15484,15 +15661,15 @@
         <v>46338</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="W2" s="28" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
@@ -15501,13 +15678,13 @@
         <v>114</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="E3" s="31" t="s">
         <v>372</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="G3" s="31" t="n">
         <v>15</v>
@@ -15543,7 +15720,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
@@ -15552,13 +15729,13 @@
         <v>116</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="E4" s="31" t="s">
         <v>372</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G4" s="31" t="n">
         <v>5</v>
@@ -15594,7 +15771,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
@@ -15603,13 +15780,13 @@
         <v>114</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="E5" s="31" t="s">
         <v>470</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>30</v>
@@ -15645,7 +15822,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
@@ -15654,13 +15831,13 @@
         <v>115</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="E6" s="31" t="s">
         <v>470</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>30</v>
@@ -15696,7 +15873,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
@@ -15705,13 +15882,13 @@
         <v>116</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="E7" s="31" t="s">
         <v>470</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>5</v>
@@ -15747,7 +15924,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>902</v>
+        <v>922</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
@@ -15756,13 +15933,13 @@
         <v>117</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="E8" s="31" t="s">
         <v>483</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>480</v>
@@ -15798,7 +15975,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -15807,13 +15984,13 @@
         <v>118</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="E9" s="31" t="s">
         <v>470</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G9" s="31" t="n">
         <v>30</v>
@@ -15849,7 +16026,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>7</v>
@@ -15858,13 +16035,13 @@
         <v>119</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="G10" s="31" t="n">
         <v>15</v>
@@ -15951,43 +16128,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>594</v>
@@ -15995,28 +16172,28 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="I2" s="28" t="n">
         <v>12</v>
@@ -16025,7 +16202,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="L2" s="29" t="n">
         <v>46340</v>
@@ -16035,30 +16212,30 @@
         <v>PASS</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
@@ -16075,25 +16252,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="H4" s="33"/>
       <c r="I4" s="33"/>
@@ -16110,25 +16287,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
@@ -16145,25 +16322,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
@@ -16180,25 +16357,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
@@ -16215,25 +16392,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>956</v>
+        <v>976</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
@@ -16250,25 +16427,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>959</v>
+        <v>979</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>961</v>
+        <v>981</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>962</v>
+        <v>982</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>963</v>
+        <v>983</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
@@ -16341,37 +16518,37 @@
         <v>140</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>964</v>
+        <v>984</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>965</v>
+        <v>985</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>589</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>968</v>
+        <v>988</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>971</v>
+        <v>991</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="M1" s="13" t="s">
         <v>594</v>
@@ -16382,13 +16559,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E2" s="30" t="n">
         <v>0.93</v>
@@ -16416,7 +16593,7 @@
         <v>46346</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>975</v>
+        <v>995</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16424,17 +16601,23 @@
         <v>5</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>976</v>
+        <v>996</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>974</v>
-      </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+        <v>994</v>
+      </c>
+      <c r="E3" s="34" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F3" s="34" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="G3" s="34" t="n">
+        <v>0.88</v>
+      </c>
       <c r="H3" s="35" t="n">
         <v>0.9</v>
       </c>
@@ -16446,27 +16629,37 @@
       </c>
       <c r="K3" s="31" t="str">
         <f aca="false">IF(OR(E3="",F3="",G3=""),"PENDING",IF(AND(E3&gt;=H3,F3&gt;=I3,G3&gt;=J3),"PASS","FAIL"))</f>
-        <v>PENDING</v>
-      </c>
-      <c r="L3" s="36"/>
-      <c r="M3" s="33"/>
+        <v>PASS</v>
+      </c>
+      <c r="L3" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>997</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>974</v>
-      </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+        <v>994</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>0.936</v>
+      </c>
+      <c r="G4" s="34" t="n">
+        <v>0.943</v>
+      </c>
       <c r="H4" s="35" t="n">
         <v>0.9</v>
       </c>
@@ -16478,23 +16671,27 @@
       </c>
       <c r="K4" s="31" t="str">
         <f aca="false">IF(OR(E4="",F4="",G4=""),"PENDING",IF(AND(E4&gt;=H4,F4&gt;=I4,G4&gt;=J4),"PASS","FAIL"))</f>
-        <v>PENDING</v>
-      </c>
-      <c r="L4" s="36"/>
-      <c r="M4" s="33"/>
+        <v>PASS</v>
+      </c>
+      <c r="L4" s="36" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>997</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -16520,13 +16717,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -16552,13 +16749,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>979</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -16584,13 +16781,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="1026">
   <si>
     <t xml:space="preserve">Meterbook — Plan, Test &amp; Reliability Tracker</t>
   </si>
@@ -2043,10 +2043,10 @@
     <t xml:space="preserve">0 high/critical findings</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeQL (security-extended; Java, Python, Actions) on every PR, main and weekly: 0 high/critical (a finding &gt;= 7.0 fails the run); Semgrep p/default on every change: 0 errors/warnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40122321805</t>
+    <t xml:space="preserve">0 open high/critical on main (code scanning). The first gate read severities from the wrong SARIF field and could not fail; fixed, it found 5 high: 2 user-controlled-bypass fixed in code, 3 CSRF-disabled excluded with reason (stateless, header-only credentials; NoAmbientCredentialsTest guards it). Semgrep p/default: 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40143497435</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-006</t>
@@ -3156,10 +3156,13 @@
     <t xml:space="preserve">identity</t>
   </si>
   <si>
-    <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40120018649</t>
+    <t xml:space="preserve">line/branch: https://github.com/mhrj7/meterbook/actions/runs/40143043993 ; mutation: https://github.com/mhrj7/meterbook/actions/runs/40120018649</t>
   </si>
   <si>
     <t xml:space="preserve">tenancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line/branch: local JaCoCo per-package (CI reports the module total); mutation: https://github.com/mhrj7/meterbook/actions/runs/40120018649</t>
   </si>
   <si>
     <t xml:space="preserve">pricing</t>
@@ -4344,54 +4347,54 @@
         <v>140</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>148</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>157</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>705</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G2" s="29" t="n">
         <v>46336</v>
@@ -4404,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L2" s="28" t="s">
         <v>599</v>
@@ -6164,31 +6167,31 @@
         <v>145</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>594</v>
@@ -8402,7 +8405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{335289DB-DB61-408A-87EF-B07A376756B3}</x14:id>
+          <x14:id>{BDB670CA-EE6E-40E6-B32A-2428B870B4B9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8416,7 +8419,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C979CEB7-F435-4329-AD6E-5EECE5235CCE}</x14:id>
+          <x14:id>{77E8D630-9192-43D1-9C10-5A837F5A5BE4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8430,7 +8433,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14D6A86A-A5CA-43DB-BABA-C785A5B749CE}</x14:id>
+          <x14:id>{55444862-616B-49CB-9C40-7274D22D20D4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8444,7 +8447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86D04ABD-1823-45B5-A3D3-DA6F2BA3C52F}</x14:id>
+          <x14:id>{8E5E5543-2094-41AF-8D1E-3DBC278DD512}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8490,7 +8493,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{335289DB-DB61-408A-87EF-B07A376756B3}">
+          <x14:cfRule type="dataBar" id="{BDB670CA-EE6E-40E6-B32A-2428B870B4B9}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8505,7 +8508,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C979CEB7-F435-4329-AD6E-5EECE5235CCE}">
+          <x14:cfRule type="dataBar" id="{77E8D630-9192-43D1-9C10-5A837F5A5BE4}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8520,7 +8523,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{14D6A86A-A5CA-43DB-BABA-C785A5B749CE}">
+          <x14:cfRule type="dataBar" id="{55444862-616B-49CB-9C40-7274D22D20D4}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8535,7 +8538,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86D04ABD-1823-45B5-A3D3-DA6F2BA3C52F}">
+          <x14:cfRule type="dataBar" id="{8E5E5543-2094-41AF-8D1E-3DBC278DD512}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10718,7 +10721,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A4B27AF6-B282-44F5-988D-F9DA739DB031}</x14:id>
+          <x14:id>{2013909B-892A-44EC-B5D0-36848A762BE4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10749,7 +10752,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A4B27AF6-B282-44F5-988D-F9DA739DB031}">
+          <x14:cfRule type="dataBar" id="{2013909B-892A-44EC-B5D0-36848A762BE4}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -14462,7 +14465,7 @@
       <c r="N47" s="33"/>
       <c r="O47" s="33"/>
     </row>
-    <row r="48" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="31" t="s">
         <v>791</v>
       </c>
@@ -14508,7 +14511,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="31" t="s">
         <v>798</v>
       </c>
@@ -16613,7 +16616,7 @@
         <v>0.974</v>
       </c>
       <c r="F3" s="34" t="n">
-        <v>0.867</v>
+        <v>0.868</v>
       </c>
       <c r="G3" s="34" t="n">
         <v>0.88</v>
@@ -16677,7 +16680,7 @@
         <v>46320</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16717,7 +16720,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>993</v>
@@ -16749,7 +16752,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>993</v>
@@ -16781,7 +16784,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>993</v>

--- a/tracker/Meterbook_Tracker.xlsx
+++ b/tracker/Meterbook_Tracker.xlsx
@@ -2151,7 +2151,7 @@
     <t xml:space="preserve">Linters in CI</t>
   </si>
   <si>
-    <t xml:space="preserve">This repo has Java, Python and shell (no Go or Rust): SpotBugs in ./gradlew check (found and fixed 5 real bugs; any finding fails), ruff and ShellCheck on every change; ci requires the job</t>
+    <t xml:space="preserve">This repo has Java, Python and shell (no Go or Rust): SpotBugs in ./gradlew check (found and fixed 5 real bugs; any finding fails), ruff and ShellCheck on every change; ci requires the job Branch protection on main requires ci, so a lint failure blocks the merge.</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/mhrj7/meterbook/actions/runs/40122321801</t>
@@ -2169,7 +2169,7 @@
     <t xml:space="preserve">Codecov</t>
   </si>
   <si>
-    <t xml:space="preserve">JaCoCo gate in ./gradlew check (90% line / 85% branch) fails the Java job and the required ci check; identity at 97.4% / 96.6%</t>
+    <t xml:space="preserve">JaCoCo gate in ./gradlew check (90% line / 85% branch) fails the Java job and the required ci check; identity at 97.4% / 96.6% Branch protection on main requires ci, so a coverage failure blocks the merge (2026-10-25).</t>
   </si>
   <si>
     <t xml:space="preserve">TC-PLT-015</t>
@@ -8405,7 +8405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDB670CA-EE6E-40E6-B32A-2428B870B4B9}</x14:id>
+          <x14:id>{E03E5F4B-BE40-4B2A-B3F0-177EFAAB297C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8419,7 +8419,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77E8D630-9192-43D1-9C10-5A837F5A5BE4}</x14:id>
+          <x14:id>{45AEEDC5-FB80-4B44-9B28-D49494EF7860}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8433,7 +8433,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55444862-616B-49CB-9C40-7274D22D20D4}</x14:id>
+          <x14:id>{20EA9846-4482-46B1-9566-E020E32FBBCB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8447,7 +8447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8E5E5543-2094-41AF-8D1E-3DBC278DD512}</x14:id>
+          <x14:id>{A24D5793-7814-4E8F-98D9-9B11BD5E8262}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8493,7 +8493,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BDB670CA-EE6E-40E6-B32A-2428B870B4B9}">
+          <x14:cfRule type="dataBar" id="{E03E5F4B-BE40-4B2A-B3F0-177EFAAB297C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8508,7 +8508,7 @@
           <xm:sqref>B14:D14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77E8D630-9192-43D1-9C10-5A837F5A5BE4}">
+          <x14:cfRule type="dataBar" id="{45AEEDC5-FB80-4B44-9B28-D49494EF7860}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8523,7 +8523,7 @@
           <xm:sqref>B22:D22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55444862-616B-49CB-9C40-7274D22D20D4}">
+          <x14:cfRule type="dataBar" id="{20EA9846-4482-46B1-9566-E020E32FBBCB}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8538,7 +8538,7 @@
           <xm:sqref>B23:D23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8E5E5543-2094-41AF-8D1E-3DBC278DD512}">
+          <x14:cfRule type="dataBar" id="{A24D5793-7814-4E8F-98D9-9B11BD5E8262}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10721,7 +10721,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2013909B-892A-44EC-B5D0-36848A762BE4}</x14:id>
+          <x14:id>{D350E4E9-1D9B-46F7-A978-9AF98DD869E0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10752,7 +10752,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2013909B-892A-44EC-B5D0-36848A762BE4}">
+          <x14:cfRule type="dataBar" id="{D350E4E9-1D9B-46F7-A978-9AF98DD869E0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13215,7 +13215,7 @@
         <v>378</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="M16" s="33" t="s">
         <v>668</v>
